--- a/ingest/2026-09-03/grandeur_airtable_upload_2026-09-03.xlsx
+++ b/ingest/2026-09-03/grandeur_airtable_upload_2026-09-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD232"/>
+  <dimension ref="A1:BF232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,6 +472,8 @@
     <col width="27" customWidth="1" min="54" max="54"/>
     <col width="19" customWidth="1" min="55" max="55"/>
     <col width="17" customWidth="1" min="56" max="56"/>
+    <col width="14" customWidth="1" min="57" max="57"/>
+    <col width="13" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -755,11 +757,21 @@
           <t>Pairs well with</t>
         </is>
       </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>MatchedRecId</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>MatchStatus</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GRNDENG-0001</t>
+          <t>ENG-GRAN-0004</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -779,7 +791,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>GRND6.5EWOBARBADOS</t>
+          <t>GRND65EWOBARBADOS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -861,13 +873,23 @@
       <c r="AV2" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>recobIv3JsQo55MFB</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GRNDENG-0002</t>
+          <t>ENG-GRAN-0001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -887,7 +909,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>GRND6.5EWOBORABORA</t>
+          <t>GRND65EWOBORABORA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -969,13 +991,23 @@
       <c r="AV3" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>recV4VUS7cqqTnyDJ</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GRNDENG-0003</t>
+          <t>ENG-GRAN-0002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -995,7 +1027,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>GRND6.5EWOSANTORINI</t>
+          <t>GRND65EWOSANTORINI</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1077,13 +1109,23 @@
       <c r="AV4" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>rec3rf57zqs0qtgdX</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GRNDENG-0004</t>
+          <t>ENG-GRAN-0005</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1103,7 +1145,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>GRND6.5EWOSARDINIA</t>
+          <t>GRND65EWOSARDINIA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1185,13 +1227,23 @@
       <c r="AV5" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>recjcchm9PeLYFCH5</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GRNDENG-0005</t>
+          <t>ENG-GRAN-0003</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1263,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>GRND6.5EWOSTLUCIA</t>
+          <t>GRND65EWOSTLUCIA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1293,13 +1345,23 @@
       <c r="AV6" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>recyY67qhu0dJtLpp</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GRNDENG-0006</t>
+          <t>ENG-GRAN-0006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1319,7 +1381,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>GRND6.5EWOTAHITI</t>
+          <t>GRND65EWOTAHITI</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1401,13 +1463,23 @@
       <c r="AV7" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>rec4CAulQKU11pPJU</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GRNDENG-0007</t>
+          <t>ENG-GRAN-0007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1427,7 +1499,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>GRND6.5EWOWHITEISLAND</t>
+          <t>GRND65EWOWHITEISLAND</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1509,13 +1581,23 @@
       <c r="AV8" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>recLO6yHFPPYvyds0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GRNDENG-0008</t>
+          <t>ENG-GRAN-0008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1617,13 +1699,23 @@
       <c r="AV9" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>recpcAoksKZkaeoV7</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GRNDENG-0009</t>
+          <t>ENG-GRAN-0009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1725,13 +1817,23 @@
       <c r="AV10" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>rectMrUUZcGqaBwlJ</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRNDENG-0010</t>
+          <t>ENG-GRAN-0012</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1751,7 +1853,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>GRND6.5HICNATURAL</t>
+          <t>GRND65NAHNATURAL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1846,13 +1948,23 @@
       <c r="BC11" t="inlineStr">
         <is>
           <t>SALE item. No regular (non-SALE) equivalent found in this price list -&gt; Cost/unit set equal to SALE price per Sale rule 3 (placeholder).</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>reczStyLrlyhpScG1</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GRNDENG-0011</t>
+          <t>ENG-GRAN-0014</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1872,7 +1984,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>GRND6.5HICHARVEST</t>
+          <t>GRND65NAHHARVEST</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1967,13 +2079,23 @@
       <c r="BC12" t="inlineStr">
         <is>
           <t>SALE item. No regular (non-SALE) equivalent found in this price list -&gt; Cost/unit set equal to SALE price per Sale rule 3 (placeholder).</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>reck5zXnzUDH3rl90</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GRNDENG-0012</t>
+          <t>ENG-GRAN-0015</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1993,7 +2115,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>GRND6.5HICMANE</t>
+          <t>GRND65NAHMANE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2088,13 +2210,23 @@
       <c r="BC13" t="inlineStr">
         <is>
           <t>SALE item. No regular (non-SALE) equivalent found in this price list -&gt; Cost/unit set equal to SALE price per Sale rule 3 (placeholder).</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>recH1Px2N8IuzEkSt</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GRNDENG-0013</t>
+          <t>ENG-GRAN-0016</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2114,7 +2246,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>GRND6.5HICNORTHWEST</t>
+          <t>GRND65NAHNORTHWEST</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2209,13 +2341,23 @@
       <c r="BC14" t="inlineStr">
         <is>
           <t>SALE item. No regular (non-SALE) equivalent found in this price list -&gt; Cost/unit set equal to SALE price per Sale rule 3 (placeholder).</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>recl8HeeCAyfimQy6</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRNDENG-0014</t>
+          <t>ENG-GRAN-0017</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2235,7 +2377,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>GRND6.5HICOWL</t>
+          <t>GRND65NAHOWL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2330,13 +2472,23 @@
       <c r="BC15" t="inlineStr">
         <is>
           <t>SALE item. No regular (non-SALE) equivalent found in this price list -&gt; Cost/unit set equal to SALE price per Sale rule 3 (placeholder).</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>recJAqKth3qlRIXfg</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GRNDENG-0015</t>
+          <t>ENG-GRAN-0018</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2356,7 +2508,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>GRND6MPLRUM</t>
+          <t>GRND6HMRUM</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2456,13 +2608,23 @@
       <c r="BC16" t="inlineStr">
         <is>
           <t>Collection marked 'while stock last' by supplier -&gt; Stock status=Clearance. SALE item with no regular equivalent -&gt; Cost/unit=SALE price per Sale rule 3.</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>recmRcirQyNypbRhi</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GRNDENG-0016</t>
+          <t>ENG-GRAN-0020</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2482,7 +2644,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>GRND7.5AOHONEYCOMB</t>
+          <t>GRND75AOHONEYCOMB</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2564,13 +2726,23 @@
       <c r="AV17" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>recMuTbvT66bH8EVB</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GRNDENG-0017</t>
+          <t>ENG-GRAN-0021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2590,7 +2762,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>GRND7.5AOSANDYSILK</t>
+          <t>GRND75AOSANDYSILK</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2672,13 +2844,23 @@
       <c r="AV18" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>rec57a5rh4YJaBS6O</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GRNDENG-0018</t>
+          <t>ENG-GRAN-0102</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2698,7 +2880,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>GRND7.5AOCASCADE</t>
+          <t>GRND75AOCASCADE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2793,13 +2975,23 @@
       <c r="BC19" t="inlineStr">
         <is>
           <t>SALE item. Regular Cost/unit ($4.59) pulled from Honeycomb/Sandy Silk in same collection/specs per Sale rule 1; SALE price $3.99 stored as Promo cost. Printed SALE row also showed $6.89 alongside $3.99 -- used regular MAP $7.19 instead; flagged for Albert to confirm whether $6.89 is a separate promo-period MAP.</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>recs0E5o3qmkZtxl5</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GRNDENG-0019</t>
+          <t>ENG-GRAN-0022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2901,13 +3093,23 @@
       <c r="AV20" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>recemCWQAxqeZ7Ozt</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GRNDENG-0020</t>
+          <t>ENG-GRAN-0023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3009,13 +3211,23 @@
       <c r="AV21" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>recvBL5tcUkb3d8BT</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GRNDENG-0021</t>
+          <t>ENG-GRAN-0024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3117,13 +3329,23 @@
       <c r="AV22" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>rec7ZKRL8HeQX37If</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GRNDENG-0022</t>
+          <t>ENG-GRAN-0025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3225,13 +3447,23 @@
       <c r="AV23" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>recowSCK0yTOmRldq</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GRNDENG-0023</t>
+          <t>ENG-GRAN-0026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3333,13 +3565,23 @@
       <c r="AV24" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE24" t="inlineStr">
+        <is>
+          <t>recrkstD4OPQqTQ3O</t>
+        </is>
+      </c>
+      <c r="BF24" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GRNDENG-0024</t>
+          <t>ENG-GRAN-0027</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3441,13 +3683,23 @@
       <c r="AV25" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE25" t="inlineStr">
+        <is>
+          <t>recjYP72KaXhttg5e</t>
+        </is>
+      </c>
+      <c r="BF25" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GRNDENG-0025</t>
+          <t>ENG-GRAN-0031</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3467,7 +3719,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>GRND7.5EWOMORAINE</t>
+          <t>GRND75EWOMORAINE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3567,13 +3819,23 @@
       <c r="BC26" t="inlineStr">
         <is>
           <t>SALE item, marked Low Stock. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3.</t>
+        </is>
+      </c>
+      <c r="BE26" t="inlineStr">
+        <is>
+          <t>recY6cnUW5RFRcTXA</t>
+        </is>
+      </c>
+      <c r="BF26" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GRNDENG-0026</t>
+          <t>ENG-GRAN-0033</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3593,7 +3855,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>GRND7.5EWOBLUEMOUNTAIN</t>
+          <t>GRND75EWOBLUEMOUNTAIN</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3688,13 +3950,23 @@
       <c r="BC27" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3.</t>
+        </is>
+      </c>
+      <c r="BE27" t="inlineStr">
+        <is>
+          <t>rec7aTuiDyoHjwL4b</t>
+        </is>
+      </c>
+      <c r="BF27" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GRNDENG-0027</t>
+          <t>ENG-GRAN-0035</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3714,7 +3986,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>GRND7.5HICALPINE</t>
+          <t>GRND75NAHALPINE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3796,13 +4068,23 @@
       <c r="AV28" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE28" t="inlineStr">
+        <is>
+          <t>rec4RaOUxSDdqk4y1</t>
+        </is>
+      </c>
+      <c r="BF28" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GRNDENG-0028</t>
+          <t>ENG-GRAN-0036</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3822,7 +4104,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>GRND7.5HICCROWN</t>
+          <t>GRND75NAHCROWN</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3904,13 +4186,23 @@
       <c r="AV29" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE29" t="inlineStr">
+        <is>
+          <t>recFRBe7ZXGsGytJl</t>
+        </is>
+      </c>
+      <c r="BF29" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GRNDENG-0029</t>
+          <t>ENG-GRAN-0037</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3930,7 +4222,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>GRND7.5HICICEFALL</t>
+          <t>GRND75NAHICEFALL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4012,13 +4304,23 @@
       <c r="AV30" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE30" t="inlineStr">
+        <is>
+          <t>recP7eLGk09wpbfq1</t>
+        </is>
+      </c>
+      <c r="BF30" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GRNDENG-0030</t>
+          <t>ENG-GRAN-0038</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4038,7 +4340,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>GRND7.5HICSUMMIT</t>
+          <t>GRND75NAHSUMMIT</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4120,13 +4422,23 @@
       <c r="AV31" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE31" t="inlineStr">
+        <is>
+          <t>recYO5qwzXD7gUVlZ</t>
+        </is>
+      </c>
+      <c r="BF31" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GRNDENG-0031</t>
+          <t>ENG-GRAN-0040</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4146,7 +4458,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>GRND7.5HICNIMBUS</t>
+          <t>GRND75NAHNIMBUS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4241,13 +4553,23 @@
       <c r="BC32" t="inlineStr">
         <is>
           <t>SALE item. Regular Cost/unit ($4.89) pulled from Alpine/Crown/Icefall/Summit in same collection/specs per Sale rule 1; SALE price $2.99 stored as Promo cost.</t>
+        </is>
+      </c>
+      <c r="BE32" t="inlineStr">
+        <is>
+          <t>recHlRL08VZ8w7xEd</t>
+        </is>
+      </c>
+      <c r="BF32" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GRNDENG-0032</t>
+          <t>ENG-GRAN-0041</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4267,7 +4589,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>GRND7.5MPLARIES</t>
+          <t>GRND75HMARIES</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4354,13 +4676,23 @@
       <c r="BC33" t="inlineStr">
         <is>
           <t>Made in Vietnam (per supplier price list).</t>
+        </is>
+      </c>
+      <c r="BE33" t="inlineStr">
+        <is>
+          <t>recWW2Mx383ZKkK8I</t>
+        </is>
+      </c>
+      <c r="BF33" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GRNDENG-0033</t>
+          <t>ENG-GRAN-0042</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4380,7 +4712,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>GRND7.5MPLLEO</t>
+          <t>GRND75HMLEO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4467,13 +4799,23 @@
       <c r="BC34" t="inlineStr">
         <is>
           <t>Made in Vietnam (per supplier price list).</t>
+        </is>
+      </c>
+      <c r="BE34" t="inlineStr">
+        <is>
+          <t>recmbZW4KfgIiDhwt</t>
+        </is>
+      </c>
+      <c r="BF34" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GRNDENG-0034</t>
+          <t>ENG-GRAN-0043</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4493,7 +4835,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>GRND7.5MPLLIBRA</t>
+          <t>GRND75HMLIBRA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4580,13 +4922,23 @@
       <c r="BC35" t="inlineStr">
         <is>
           <t>Made in Vietnam (per supplier price list).</t>
+        </is>
+      </c>
+      <c r="BE35" t="inlineStr">
+        <is>
+          <t>rech5HHte9DpIc1FJ</t>
+        </is>
+      </c>
+      <c r="BF35" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GRNDENG-0035</t>
+          <t>ENG-GRAN-0044</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4606,7 +4958,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>GRND7.5MPLTAURUS</t>
+          <t>GRND75HMTAURUS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4693,13 +5045,23 @@
       <c r="BC36" t="inlineStr">
         <is>
           <t>Made in Vietnam (per supplier price list).</t>
+        </is>
+      </c>
+      <c r="BE36" t="inlineStr">
+        <is>
+          <t>recPLxBPuIp4ShUzV</t>
+        </is>
+      </c>
+      <c r="BF36" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GRNDENG-0036</t>
+          <t>ENG-GRAN-0045</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4719,7 +5081,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>GRND7.5MPLSCORPIO</t>
+          <t>GRND75HMSCORPIO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4806,13 +5168,23 @@
       <c r="BC37" t="inlineStr">
         <is>
           <t>Made in Vietnam (per supplier price list).</t>
+        </is>
+      </c>
+      <c r="BE37" t="inlineStr">
+        <is>
+          <t>reczw6QoXkdGMIpcH</t>
+        </is>
+      </c>
+      <c r="BF37" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GRNDENG-0037</t>
+          <t>ENG-GRAN-0046</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4832,7 +5204,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>GRND7.5MPLTHUNDERCLOUD</t>
+          <t>GRND75HMTHUNDERCLOUD</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4927,13 +5299,23 @@
       <c r="BC38" t="inlineStr">
         <is>
           <t>Made in Vietnam. SALE item. Regular Cost/unit ($4.89) pulled from same collection/specs per Sale rule 1; SALE price $3.99 stored as Promo cost.</t>
+        </is>
+      </c>
+      <c r="BE38" t="inlineStr">
+        <is>
+          <t>recW9DF0ONezbBXT3</t>
+        </is>
+      </c>
+      <c r="BF38" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GRNDENG-0038</t>
+          <t>ENG-GRAN-0047</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4953,7 +5335,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>GRND7.5EWOCLIFF</t>
+          <t>GRND75EWOCLIFF</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5035,13 +5417,23 @@
       <c r="AV39" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE39" t="inlineStr">
+        <is>
+          <t>recccHtX6HCdB3hgc</t>
+        </is>
+      </c>
+      <c r="BF39" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GRNDENG-0039</t>
+          <t>ENG-GRAN-0048</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5061,7 +5453,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>GRND7.5EWOPETRICHOR</t>
+          <t>GRND75EWOPETRICHOR</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5143,13 +5535,23 @@
       <c r="AV40" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE40" t="inlineStr">
+        <is>
+          <t>recrDEm9SKKDRdH0S</t>
+        </is>
+      </c>
+      <c r="BF40" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GRNDENG-0040</t>
+          <t>ENG-GRAN-0049</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5169,7 +5571,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>GRND7.5EWOSTRATUS</t>
+          <t>GRND75EWOSTRATUS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5251,13 +5653,23 @@
       <c r="AV41" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE41" t="inlineStr">
+        <is>
+          <t>rec2Nw4bOwpYj4pB2</t>
+        </is>
+      </c>
+      <c r="BF41" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GRNDENG-0041</t>
+          <t>ENG-GRAN-0050</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5277,7 +5689,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>GRND7.5EWOLAGOM</t>
+          <t>GRND75EWOLAGOM</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5359,13 +5771,23 @@
       <c r="AV42" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE42" t="inlineStr">
+        <is>
+          <t>reccc1KaMtXjAZUgq</t>
+        </is>
+      </c>
+      <c r="BF42" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GRNDENG-0042</t>
+          <t>ENG-GRAN-0051</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5385,7 +5807,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>GRND7.5EWONORDICSAND</t>
+          <t>GRND75EWONORDICSAND</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5467,13 +5889,23 @@
       <c r="AV43" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE43" t="inlineStr">
+        <is>
+          <t>recU1iy6tJ8UCHeND</t>
+        </is>
+      </c>
+      <c r="BF43" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GRNDENG-0043</t>
+          <t>ENG-GRAN-0052</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5493,7 +5925,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>GRND7.5EWOPANDO</t>
+          <t>GRND75EWOPANDO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5575,13 +6007,23 @@
       <c r="AV44" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE44" t="inlineStr">
+        <is>
+          <t>recfr7LFYZ6SGI54n</t>
+        </is>
+      </c>
+      <c r="BF44" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GRNDENG-0044</t>
+          <t>ENG-GRAN-0053</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5601,7 +6043,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>GRND7.5EWOTUNDRA</t>
+          <t>GRND75EWOTUNDRA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5683,13 +6125,23 @@
       <c r="AV45" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE45" t="inlineStr">
+        <is>
+          <t>recioIeirkqlQufUk</t>
+        </is>
+      </c>
+      <c r="BF45" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GRNDENG-0045</t>
+          <t>ENG-GRAN-0054</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5709,7 +6161,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>GRND7.5EWOKINGSLANDING</t>
+          <t>GRND75EWOKINGSLANDING</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5791,13 +6243,23 @@
       <c r="AV46" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE46" t="inlineStr">
+        <is>
+          <t>recvWKnECA0TM1IMi</t>
+        </is>
+      </c>
+      <c r="BF46" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GRNDENG-0046</t>
+          <t>ENG-GRAN-0055</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5817,7 +6279,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>GRND7.5EWOSUNSPEAR</t>
+          <t>GRND75EWOSUNSPEAR</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5899,13 +6361,23 @@
       <c r="AV47" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE47" t="inlineStr">
+        <is>
+          <t>rec8DD6k0xiTO1EOL</t>
+        </is>
+      </c>
+      <c r="BF47" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GRNDENG-0047</t>
+          <t>ENG-GRAN-0056</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6012,13 +6484,23 @@
       <c r="AV48" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE48" t="inlineStr">
+        <is>
+          <t>recvO3jbq9ZxWaDKp</t>
+        </is>
+      </c>
+      <c r="BF48" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GRNDENG-0048</t>
+          <t>ENG-GRAN-0057</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6125,13 +6607,23 @@
       <c r="AV49" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE49" t="inlineStr">
+        <is>
+          <t>recl4vvGDFjjQp4wT</t>
+        </is>
+      </c>
+      <c r="BF49" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GRNDENG-0049</t>
+          <t>ENG-GRAN-0058</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6238,13 +6730,23 @@
       <c r="AV50" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE50" t="inlineStr">
+        <is>
+          <t>recHby5PmGX4EcM9R</t>
+        </is>
+      </c>
+      <c r="BF50" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GRNDENG-0050</t>
+          <t>ENG-GRAN-0059</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6351,13 +6853,23 @@
       <c r="AV51" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE51" t="inlineStr">
+        <is>
+          <t>recENSL6XA7o5bqDM</t>
+        </is>
+      </c>
+      <c r="BF51" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GRNDENG-0051</t>
+          <t>ENG-GRAN-0060</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6464,13 +6976,23 @@
       <c r="AV52" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE52" t="inlineStr">
+        <is>
+          <t>rec8qIS5GbTbsNTpE</t>
+        </is>
+      </c>
+      <c r="BF52" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GRNDENG-0052</t>
+          <t>ENG-GRAN-0061</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6490,7 +7012,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>GRND9.5EWOBANFF</t>
+          <t>GRND95EWOBANFF</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6577,13 +7099,23 @@
       <c r="AV53" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE53" t="inlineStr">
+        <is>
+          <t>recOyszODJ2Gb4jbQ</t>
+        </is>
+      </c>
+      <c r="BF53" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GRNDENG-0053</t>
+          <t>ENG-GRAN-0062</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6603,7 +7135,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>GRND9.5EWOCAPEBRETON</t>
+          <t>GRND95EWOCAPEBRETON</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6690,13 +7222,23 @@
       <c r="AV54" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE54" t="inlineStr">
+        <is>
+          <t>rec2dCVugoy6SVmMC</t>
+        </is>
+      </c>
+      <c r="BF54" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GRNDENG-0054</t>
+          <t>ENG-GRAN-0063</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6716,7 +7258,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>GRND9.5EWOMONTTREMBLANT</t>
+          <t>GRND95EWOMONTTREMBLANT</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6803,13 +7345,23 @@
       <c r="AV55" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE55" t="inlineStr">
+        <is>
+          <t>rectOV4YtmMPmtLtp</t>
+        </is>
+      </c>
+      <c r="BF55" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GRNDENG-0055</t>
+          <t>ENG-GRAN-0064</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6829,7 +7381,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>GRND9.5EWOPACIFICRIM</t>
+          <t>GRND95EWOPACIFICRIM</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6916,13 +7468,23 @@
       <c r="AV56" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE56" t="inlineStr">
+        <is>
+          <t>recrMxRXow9gnjj0s</t>
+        </is>
+      </c>
+      <c r="BF56" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GRNDENG-0056</t>
+          <t>ENG-GRAN-0065</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6942,7 +7504,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>GRND9.5EWOWHISTLER</t>
+          <t>GRND95EWOWHISTLER</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7029,13 +7591,23 @@
       <c r="AV57" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE57" t="inlineStr">
+        <is>
+          <t>rec5wHCyumqqqUaZ2</t>
+        </is>
+      </c>
+      <c r="BF57" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GRNDENG-0057</t>
+          <t>ENG-GRAN-0066</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7055,7 +7627,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>GRND9.5EWOYOHO</t>
+          <t>GRND95EWOYOHO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -7142,13 +7714,23 @@
       <c r="AV58" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE58" t="inlineStr">
+        <is>
+          <t>recq8zYjWbpIZkRWd</t>
+        </is>
+      </c>
+      <c r="BF58" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GRNDENG-0058</t>
+          <t>ENG-GRAN-0071</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7168,7 +7750,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>GRND7.5EWOSANDBAR75</t>
+          <t>GRND75EWOSANDBAR</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7250,13 +7832,23 @@
       <c r="AV59" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE59" t="inlineStr">
+        <is>
+          <t>rec6xHThpe9i4sVux</t>
+        </is>
+      </c>
+      <c r="BF59" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GRNDENG-0059</t>
+          <t>ENG-GRAN-0072</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7276,7 +7868,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>GRND7.5EWOSILVA75</t>
+          <t>GRND75EWOSILVA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7358,13 +7950,23 @@
       <c r="AV60" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE60" t="inlineStr">
+        <is>
+          <t>recrgrGzGOAuMU4IF</t>
+        </is>
+      </c>
+      <c r="BF60" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GRNDENG-0060</t>
+          <t>ENG-GRAN-0069</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7384,7 +7986,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>GRND7.5EWOANACAPRI75</t>
+          <t>GRND75EWOANACAPRI</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7479,13 +8081,23 @@
       <c r="BC61" t="inlineStr">
         <is>
           <t>SALE item (footnote 1 = AB Grade). No regular equivalent in this collection at this grade/finish combo -&gt; Cost/unit=SALE price per Sale rule 3.</t>
+        </is>
+      </c>
+      <c r="BE61" t="inlineStr">
+        <is>
+          <t>rec5DMsOWZXnpiqVt</t>
+        </is>
+      </c>
+      <c r="BF61" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GRNDENG-0061</t>
+          <t>ENG-GRAN-0070</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7505,7 +8117,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>GRND7.5EWOMILAN75</t>
+          <t>GRND75EWOMILAN</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7600,13 +8212,23 @@
       <c r="BC62" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection at this grade/finish combo -&gt; Cost/unit=SALE price per Sale rule 3.</t>
+        </is>
+      </c>
+      <c r="BE62" t="inlineStr">
+        <is>
+          <t>rec6yYynTfTgr4Js2</t>
+        </is>
+      </c>
+      <c r="BF62" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GRNDENG-0062</t>
+          <t>ENG-GRAN-0073</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7626,7 +8248,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>GRND7.5EWOAZURECOAST75</t>
+          <t>GRND75EWOAZURECOAST</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7721,13 +8343,23 @@
       <c r="BC63" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection at this grade/finish combo -&gt; Cost/unit=SALE price per Sale rule 3.</t>
+        </is>
+      </c>
+      <c r="BE63" t="inlineStr">
+        <is>
+          <t>rec6l7tsFUidrXZQs</t>
+        </is>
+      </c>
+      <c r="BF63" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GRNDENG-0063</t>
+          <t>ENG-GRAN-0074</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7747,7 +8379,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>GRND7.5EWOMOROCCOSAND75</t>
+          <t>GRND75EWOMOROCCOSAND</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7842,13 +8474,23 @@
       <c r="BC64" t="inlineStr">
         <is>
           <t>SALE item, same price row as Azure Coast (7.5"). No regular equivalent -&gt; Cost/unit=SALE price per Sale rule 3.</t>
+        </is>
+      </c>
+      <c r="BE64" t="inlineStr">
+        <is>
+          <t>recdxuD6iP0RZXriG</t>
+        </is>
+      </c>
+      <c r="BF64" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GRNDENG-0064</t>
+          <t>ENG-GRAN-0075</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7868,7 +8510,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>GRND6EWOMOROCCOSAND6</t>
+          <t>GRND6EWOMOROCCOSAND</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7963,13 +8605,23 @@
       <c r="BC65" t="inlineStr">
         <is>
           <t>SALE item (footnote 2 = ABCD Grade). No regular equivalent at this width/grade -&gt; Cost/unit=SALE price per Sale rule 3.</t>
+        </is>
+      </c>
+      <c r="BE65" t="inlineStr">
+        <is>
+          <t>recyyAL9tTZULI15J</t>
+        </is>
+      </c>
+      <c r="BF65" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>GRNDENG-0065</t>
+          <t>ENG-GRAN-0076</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7989,7 +8641,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>GRND6EWOBAROSSA6</t>
+          <t>GRND6EWOBAROSSA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8071,13 +8723,23 @@
       <c r="AV66" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE66" t="inlineStr">
+        <is>
+          <t>recfMCLAfUHMITcOJ</t>
+        </is>
+      </c>
+      <c r="BF66" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GRNDENG-0066</t>
+          <t>ENG-GRAN-0077</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8097,7 +8759,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>GRND6EWOBURGUNDY6</t>
+          <t>GRND6EWOBURGUNDY</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8179,13 +8841,23 @@
       <c r="AV67" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE67" t="inlineStr">
+        <is>
+          <t>recE8fcQMenQgy9nC</t>
+        </is>
+      </c>
+      <c r="BF67" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GRNDENG-0067</t>
+          <t>ENG-GRAN-0078</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -8205,7 +8877,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>GRND6EWONAPAVALLEY6</t>
+          <t>GRND6EWONAPAVALLEY</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8287,13 +8959,23 @@
       <c r="AV68" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE68" t="inlineStr">
+        <is>
+          <t>rece1qC7ekum7jbPQ</t>
+        </is>
+      </c>
+      <c r="BF68" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GRNDENG-0068</t>
+          <t>ENG-GRAN-0079</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -8313,7 +8995,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>GRND6EWOSONOMA6</t>
+          <t>GRND6EWOSONOMA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8395,13 +9077,23 @@
       <c r="AV69" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE69" t="inlineStr">
+        <is>
+          <t>recopArVtH3EsiT3h</t>
+        </is>
+      </c>
+      <c r="BF69" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GRNDENG-0069</t>
+          <t>ENG-GRAN-0103</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -8421,7 +9113,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>GRND6EWOVENETO6</t>
+          <t>GRND6EWOVENETO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8503,13 +9195,23 @@
       <c r="AV70" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>NEW PRODUCT — not present in the live Master Flooring Catalogue on 2026-09-03. SKU ENG-GRAN-0103 assigned continuing the live ENG-GRAN sequence.</t>
+        </is>
+      </c>
+      <c r="BF70" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GRNDENG-0070</t>
+          <t>ENG-GRAN-0080</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8529,7 +9231,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>GRND7.5EWOBAROSSA75</t>
+          <t>GRND75EWOBAROSSA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8611,13 +9313,23 @@
       <c r="AV71" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE71" t="inlineStr">
+        <is>
+          <t>recGAMmF7fXCnX0mu</t>
+        </is>
+      </c>
+      <c r="BF71" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GRNDENG-0071</t>
+          <t>ENG-GRAN-0081</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8637,7 +9349,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>GRND7.5EWOBURGUNDY75</t>
+          <t>GRND75EWOBURGUNDY</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8719,13 +9431,23 @@
       <c r="AV72" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE72" t="inlineStr">
+        <is>
+          <t>recVLY1ltYASjMNH1</t>
+        </is>
+      </c>
+      <c r="BF72" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GRNDENG-0072</t>
+          <t>ENG-GRAN-0082</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8745,7 +9467,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>GRND7.5EWONAPAVALLEY75</t>
+          <t>GRND75EWONAPAVALLEY</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8827,13 +9549,23 @@
       <c r="AV73" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE73" t="inlineStr">
+        <is>
+          <t>recjxE4E1ytHQudWG</t>
+        </is>
+      </c>
+      <c r="BF73" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GRNDENG-0073</t>
+          <t>ENG-GRAN-0083</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8853,7 +9585,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>GRND7.5EWOSONOMA75</t>
+          <t>GRND75EWOSONOMA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8935,13 +9667,23 @@
       <c r="AV74" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE74" t="inlineStr">
+        <is>
+          <t>recANpOyJTXSRtEmP</t>
+        </is>
+      </c>
+      <c r="BF74" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GRNDENG-0074</t>
+          <t>ENG-GRAN-0104</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8961,7 +9703,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>GRND7.5EWOVENETO75</t>
+          <t>GRND75EWOVENETO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9043,13 +9785,23 @@
       <c r="AV75" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>NEW PRODUCT — not present in the live Master Flooring Catalogue on 2026-09-03. SKU ENG-GRAN-0104 assigned continuing the live ENG-GRAN sequence.</t>
+        </is>
+      </c>
+      <c r="BF75" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GRNDENG-0075</t>
+          <t>ENG-GRAN-0084</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9156,13 +9908,23 @@
       <c r="AV76" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE76" t="inlineStr">
+        <is>
+          <t>rec1ImzgiQHXtltx4</t>
+        </is>
+      </c>
+      <c r="BF76" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GRNDENG-0076</t>
+          <t>ENG-GRAN-0085</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9269,13 +10031,23 @@
       <c r="AV77" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE77" t="inlineStr">
+        <is>
+          <t>reco4PsH4XFZGKbDB</t>
+        </is>
+      </c>
+      <c r="BF77" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GRNDENG-0077</t>
+          <t>ENG-GRAN-0086</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9382,13 +10154,23 @@
       <c r="AV78" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE78" t="inlineStr">
+        <is>
+          <t>recZkh8hsWRQKpRIi</t>
+        </is>
+      </c>
+      <c r="BF78" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GRNDENG-0078</t>
+          <t>ENG-GRAN-0087</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9495,13 +10277,23 @@
       <c r="AV79" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE79" t="inlineStr">
+        <is>
+          <t>recnb6n9H5Yy1ySzT</t>
+        </is>
+      </c>
+      <c r="BF79" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GRNDENG-0079</t>
+          <t>ENG-GRAN-0091</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9521,7 +10313,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>GRND7.5AOROSEDALE</t>
+          <t>GRND75AOROSEDALE</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9603,13 +10395,23 @@
       <c r="AV80" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE80" t="inlineStr">
+        <is>
+          <t>recSQSHDfAheVBlYd</t>
+        </is>
+      </c>
+      <c r="BF80" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GRNDENG-0080</t>
+          <t>ENG-GRAN-0094</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9716,13 +10518,23 @@
       <c r="BC81" t="inlineStr">
         <is>
           <t>Species stated generically as 'White Oak' on supplier price list, not specified American or European. Stored verbatim; confirm exact species with Grandeur rep.</t>
+        </is>
+      </c>
+      <c r="BE81" t="inlineStr">
+        <is>
+          <t>reclc44VA0WIZb8FA</t>
+        </is>
+      </c>
+      <c r="BF81" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>GRNDENG-0081</t>
+          <t>ENG-GRAN-0095</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9829,13 +10641,23 @@
       <c r="BC82" t="inlineStr">
         <is>
           <t>Species stated generically as 'White Oak' on supplier price list, not specified American or European. Stored verbatim; confirm exact species with Grandeur rep.</t>
+        </is>
+      </c>
+      <c r="BE82" t="inlineStr">
+        <is>
+          <t>recn8gFvjHu3L0X6H</t>
+        </is>
+      </c>
+      <c r="BF82" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GRNDENG-0082</t>
+          <t>ENG-GRAN-0096</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9942,13 +10764,23 @@
       <c r="BC83" t="inlineStr">
         <is>
           <t>Species stated generically as 'White Oak' on supplier price list, not specified American or European. Stored verbatim; confirm exact species with Grandeur rep.</t>
+        </is>
+      </c>
+      <c r="BE83" t="inlineStr">
+        <is>
+          <t>recD126B8LyUIyvCI</t>
+        </is>
+      </c>
+      <c r="BF83" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GRNDENG-0083</t>
+          <t>ENG-GRAN-0097</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10055,13 +10887,23 @@
       <c r="BC84" t="inlineStr">
         <is>
           <t>Species stated generically as 'White Oak' on supplier price list, not specified American or European. Stored verbatim; confirm exact species with Grandeur rep.</t>
+        </is>
+      </c>
+      <c r="BE84" t="inlineStr">
+        <is>
+          <t>recOINE0AOuUGKSpu</t>
+        </is>
+      </c>
+      <c r="BF84" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GRNDENG-0084</t>
+          <t>ENG-GRAN-0098</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10081,7 +10923,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>GRND7.5WOBRONZEDUST</t>
+          <t>GRND75WOBRONZEDUST</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -10163,13 +11005,23 @@
       <c r="BC85" t="inlineStr">
         <is>
           <t>FLAG FOR ALBERT: Grade printed as 'BCDE Grade' -- does not map to standard letter grades (AB/ABC/ABCD/EF) or a canonical word grade. Grade field left blank pending supplier clarification; verbatim supplier grade: BCDE. Species also stated generically as 'White Oak' (American/European unspecified).</t>
+        </is>
+      </c>
+      <c r="BE85" t="inlineStr">
+        <is>
+          <t>recYXJ4NR4d4EC2sS</t>
+        </is>
+      </c>
+      <c r="BF85" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GRNDENG-0085</t>
+          <t>ENG-GRAN-0099</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10189,7 +11041,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>GRND7.5WOCARRARA</t>
+          <t>GRND75WOCARRARA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -10271,13 +11123,23 @@
       <c r="BC86" t="inlineStr">
         <is>
           <t>FLAG FOR ALBERT: Grade printed as 'BCDE Grade' -- does not map to standard letter grades (AB/ABC/ABCD/EF) or a canonical word grade. Grade field left blank pending supplier clarification; verbatim supplier grade: BCDE. Species also stated generically as 'White Oak' (American/European unspecified).</t>
+        </is>
+      </c>
+      <c r="BE86" t="inlineStr">
+        <is>
+          <t>rectITu7Lvdsw0NZd</t>
+        </is>
+      </c>
+      <c r="BF86" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GRNDENG-0086</t>
+          <t>ENG-GRAN-0100</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10297,7 +11159,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>GRND7.5WOCLAYBORN</t>
+          <t>GRND75WOCLAYBORN</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -10379,13 +11241,23 @@
       <c r="BC87" t="inlineStr">
         <is>
           <t>FLAG FOR ALBERT: Grade printed as 'BCDE Grade' -- does not map to standard letter grades (AB/ABC/ABCD/EF) or a canonical word grade. Grade field left blank pending supplier clarification; verbatim supplier grade: BCDE. Species also stated generically as 'White Oak' (American/European unspecified).</t>
+        </is>
+      </c>
+      <c r="BE87" t="inlineStr">
+        <is>
+          <t>recqAw5bAaIuBXPDu</t>
+        </is>
+      </c>
+      <c r="BF87" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GRNDENG-0087</t>
+          <t>ENG-GRAN-0101</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10405,7 +11277,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>GRND7.5WOTERRACOTTA</t>
+          <t>GRND75WOTERRACOTTA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -10487,13 +11359,23 @@
       <c r="BC88" t="inlineStr">
         <is>
           <t>FLAG FOR ALBERT: Grade printed as 'BCDE Grade' -- does not map to standard letter grades (AB/ABC/ABCD/EF) or a canonical word grade. Grade field left blank pending supplier clarification; verbatim supplier grade: BCDE. Species also stated generically as 'White Oak' (American/European unspecified).</t>
+        </is>
+      </c>
+      <c r="BE88" t="inlineStr">
+        <is>
+          <t>recf2rwzPba5pfr4B</t>
+        </is>
+      </c>
+      <c r="BF88" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GRNDENG-0088</t>
+          <t>ENG-GRAN-0105</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10513,7 +11395,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>GRND6WOCAMBRIDGEWILLOW6</t>
+          <t>GRND6WOCAMBRIDGEWILLOW</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -10599,14 +11481,19 @@
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>Species stated generically as 'White Oak' on supplier price list, not specified American or European. Stored verbatim; confirm exact species with Grandeur rep.</t>
+          <t>NEW PRODUCT — not present in the live Master Flooring Catalogue on 2026-09-03. SKU ENG-GRAN-0105 assigned continuing the live ENG-GRAN sequence. | Species stated generically as 'White Oak' on supplier price list, not specified American or European. Stored verbatim; confirm exact species with Grandeur rep.</t>
+        </is>
+      </c>
+      <c r="BF89" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GRNDENG-0089</t>
+          <t>ENG-GRAN-0106</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10626,7 +11513,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>GRND6WOGLASGOWROCKS6</t>
+          <t>GRND6WOGLASGOWROCKS</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -10712,14 +11599,19 @@
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>Species stated generically as 'White Oak' on supplier price list, not specified American or European. Stored verbatim; confirm exact species with Grandeur rep.</t>
+          <t>NEW PRODUCT — not present in the live Master Flooring Catalogue on 2026-09-03. SKU ENG-GRAN-0106 assigned continuing the live ENG-GRAN sequence. | Species stated generically as 'White Oak' on supplier price list, not specified American or European. Stored verbatim; confirm exact species with Grandeur rep.</t>
+        </is>
+      </c>
+      <c r="BF90" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>GRNDENG-0090</t>
+          <t>ENG-GRAN-0107</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10739,7 +11631,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>GRND6WOLONDONFOG6</t>
+          <t>GRND6WOLONDONFOG</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -10825,14 +11717,19 @@
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>Species stated generically as 'White Oak' on supplier price list, not specified American or European. Stored verbatim; confirm exact species with Grandeur rep.</t>
+          <t>NEW PRODUCT — not present in the live Master Flooring Catalogue on 2026-09-03. SKU ENG-GRAN-0107 assigned continuing the live ENG-GRAN sequence. | Species stated generically as 'White Oak' on supplier price list, not specified American or European. Stored verbatim; confirm exact species with Grandeur rep.</t>
+        </is>
+      </c>
+      <c r="BF91" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GRNDENG-0091</t>
+          <t>ENG-GRAN-0108</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10852,7 +11749,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>GRND6WOOXFORDSTONE6</t>
+          <t>GRND6WOOXFORDSTONE</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -10938,14 +11835,19 @@
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>Species stated generically as 'White Oak' on supplier price list, not specified American or European. Stored verbatim; confirm exact species with Grandeur rep.</t>
+          <t>NEW PRODUCT — not present in the live Master Flooring Catalogue on 2026-09-03. SKU ENG-GRAN-0108 assigned continuing the live ENG-GRAN sequence. | Species stated generically as 'White Oak' on supplier price list, not specified American or European. Stored verbatim; confirm exact species with Grandeur rep.</t>
+        </is>
+      </c>
+      <c r="BF92" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>GRNDENG-0092</t>
+          <t>ENG-GRAN-0109</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10965,7 +11867,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>GRND7.5WOCAMBRIDGEWILLOW75</t>
+          <t>GRND75WOCAMBRIDGEWILLOW</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -11051,14 +11953,19 @@
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>Species stated generically as 'White Oak' on supplier price list, not specified American or European. Stored verbatim; confirm exact species with Grandeur rep.</t>
+          <t>NEW PRODUCT — not present in the live Master Flooring Catalogue on 2026-09-03. SKU ENG-GRAN-0109 assigned continuing the live ENG-GRAN sequence. | Species stated generically as 'White Oak' on supplier price list, not specified American or European. Stored verbatim; confirm exact species with Grandeur rep.</t>
+        </is>
+      </c>
+      <c r="BF93" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GRNDENG-0093</t>
+          <t>ENG-GRAN-0110</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -11078,7 +11985,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>GRND7.5WOGLASGOWROCKS75</t>
+          <t>GRND75WOGLASGOWROCKS</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -11164,14 +12071,19 @@
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>Species stated generically as 'White Oak' on supplier price list, not specified American or European. Stored verbatim; confirm exact species with Grandeur rep.</t>
+          <t>NEW PRODUCT — not present in the live Master Flooring Catalogue on 2026-09-03. SKU ENG-GRAN-0110 assigned continuing the live ENG-GRAN sequence. | Species stated generically as 'White Oak' on supplier price list, not specified American or European. Stored verbatim; confirm exact species with Grandeur rep.</t>
+        </is>
+      </c>
+      <c r="BF94" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GRNDENG-0094</t>
+          <t>ENG-GRAN-0111</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -11191,7 +12103,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>GRND7.5WOLONDONFOG75</t>
+          <t>GRND75WOLONDONFOG</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -11277,14 +12189,19 @@
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>Species stated generically as 'White Oak' on supplier price list, not specified American or European. Stored verbatim; confirm exact species with Grandeur rep.</t>
+          <t>NEW PRODUCT — not present in the live Master Flooring Catalogue on 2026-09-03. SKU ENG-GRAN-0111 assigned continuing the live ENG-GRAN sequence. | Species stated generically as 'White Oak' on supplier price list, not specified American or European. Stored verbatim; confirm exact species with Grandeur rep.</t>
+        </is>
+      </c>
+      <c r="BF95" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GRNDENG-0095</t>
+          <t>ENG-GRAN-0112</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -11304,7 +12221,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>GRND7.5WOOXFORDSTONE75</t>
+          <t>GRND75WOOXFORDSTONE</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -11390,14 +12307,19 @@
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>Species stated generically as 'White Oak' on supplier price list, not specified American or European. Stored verbatim; confirm exact species with Grandeur rep.</t>
+          <t>NEW PRODUCT — not present in the live Master Flooring Catalogue on 2026-09-03. SKU ENG-GRAN-0112 assigned continuing the live ENG-GRAN sequence. | Species stated generically as 'White Oak' on supplier price list, not specified American or European. Stored verbatim; confirm exact species with Grandeur rep.</t>
+        </is>
+      </c>
+      <c r="BF96" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GRNDHWD-0001</t>
+          <t>HWD-GRAN-0001</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -11417,7 +12339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>GRND4.25ROAMARETTO</t>
+          <t>GRND425NAROAMARETTO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -11491,13 +12413,23 @@
       <c r="AV97" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE97" t="inlineStr">
+        <is>
+          <t>recJEAui04CEgvXk1</t>
+        </is>
+      </c>
+      <c r="BF97" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>GRNDHWD-0002</t>
+          <t>HWD-GRAN-0002</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11517,7 +12449,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>GRND4.25ROGUNSTOCK</t>
+          <t>GRND425NAROGUNSTOCK</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -11591,13 +12523,23 @@
       <c r="AV98" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE98" t="inlineStr">
+        <is>
+          <t>recg1PrBGLH0yGOSP</t>
+        </is>
+      </c>
+      <c r="BF98" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>GRNDHWD-0003</t>
+          <t>HWD-GRAN-0003</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -11617,7 +12559,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>GRND4.25ROLATTE</t>
+          <t>GRND425NAROLATTE</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -11691,13 +12633,23 @@
       <c r="AV99" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE99" t="inlineStr">
+        <is>
+          <t>recGdy9BlOqgcHKjt</t>
+        </is>
+      </c>
+      <c r="BF99" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GRNDHWD-0004</t>
+          <t>HWD-GRAN-0004</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11717,7 +12669,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>GRND4.25ROMOKA</t>
+          <t>GRND425NAROMOKA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -11791,13 +12743,23 @@
       <c r="AV100" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE100" t="inlineStr">
+        <is>
+          <t>recStjq9Q4MDWhdMm</t>
+        </is>
+      </c>
+      <c r="BF100" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>GRNDHWD-0005</t>
+          <t>HWD-GRAN-0005</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -11817,7 +12779,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>GRND4.25ROTREEBARK</t>
+          <t>GRND425NAROTREEBARK</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -11891,13 +12853,23 @@
       <c r="AV101" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE101" t="inlineStr">
+        <is>
+          <t>rec9h3qlnQmOCA6PJ</t>
+        </is>
+      </c>
+      <c r="BF101" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>GRNDHWD-0006</t>
+          <t>HWD-GRAN-0006</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11917,7 +12889,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>GRND4.25ROWALNUT</t>
+          <t>GRND425NAROWALNUT</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -11991,13 +12963,23 @@
       <c r="AV102" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE102" t="inlineStr">
+        <is>
+          <t>recw6LxynLxHtJn4Z</t>
+        </is>
+      </c>
+      <c r="BF102" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>GRNDLVP-0001</t>
+          <t>SPC-GRAN-0003</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -12022,7 +13004,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>GRNDATLANTICCDW3402</t>
+          <t>GRND7ATLANTICCDW3402</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -12123,6 +13105,16 @@
       <c r="BC103" t="inlineStr">
         <is>
           <t>Colour name not provided by supplier -- product identified only by code 'CDW340-2'. Used as colour placeholder; confirm actual colour name with Grandeur. SALE item, no regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 4.0mm SPC + 1mm underpad (material not named). *Two-side Closed Treads Available.</t>
+        </is>
+      </c>
+      <c r="BE103" t="inlineStr">
+        <is>
+          <t>recGGICeEf2UhHchV</t>
+        </is>
+      </c>
+      <c r="BF103" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
@@ -12154,7 +13146,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>GRNDATLANTIC8936</t>
+          <t>GRND7ATLANTIC8936</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -12254,14 +13246,19 @@
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>Colour name not provided by supplier -- product identified only by code '8936'. Used as colour placeholder; confirm actual colour name with Grandeur. SALE item, no regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 4.0mm SPC + 1mm underpad (material not named). *Two-side Closed Treads Available.</t>
+          <t>AMBIGUOUS MATCH — could not be reconciled against the live catalogue with confidence; SKU below is the run-generated placeholder, NOT a real catalogue SKU. Colour placeholder "8936" vs live "GF8936" (SPC-GRAN-0001, Supplier SKU GF8936). Partial supplier-code match only — not confident enough to adopt. Confirm with Grandeur, then either adopt SPC-GRAN-0001 or keep as new. Resolve before import. | Colour name not provided by supplier -- product identified only by code '8936'. Used as colour placeholder; confirm actual colour name with Grandeur. SALE item, no regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 4.0mm SPC + 1mm underpad (material not named). *Two-side Closed Treads Available.</t>
+        </is>
+      </c>
+      <c r="BF104" t="inlineStr">
+        <is>
+          <t>ambiguous</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>GRNDLVP-0003</t>
+          <t>SPC-GRAN-0007</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -12281,7 +13278,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>GRNDCONTINENCONNECTICUT70MM</t>
+          <t>GRND7CONTINENTALCONNECTICUT</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -12387,13 +13384,23 @@
       <c r="BC105" t="inlineStr">
         <is>
           <t>SALE item ('7.0 only'). No regular equivalent in this tier -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named). Marked Low Stock.</t>
+        </is>
+      </c>
+      <c r="BE105" t="inlineStr">
+        <is>
+          <t>rec4iGhXwJqPMTCDz</t>
+        </is>
+      </c>
+      <c r="BF105" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>GRNDLVP-0004</t>
+          <t>SPC-GRAN-0009</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -12413,7 +13420,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>GRNDCONTINENIOWA70MM</t>
+          <t>GRND7CONTINENTALIOWA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -12514,13 +13521,23 @@
       <c r="BC106" t="inlineStr">
         <is>
           <t>SALE item ('7.0 only'). No regular equivalent in this tier -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named).</t>
+        </is>
+      </c>
+      <c r="BE106" t="inlineStr">
+        <is>
+          <t>recAlS3YvS63oICP7</t>
+        </is>
+      </c>
+      <c r="BF106" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GRNDLVP-0005</t>
+          <t>SPC-GRAN-0010</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -12540,7 +13557,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>GRNDCONTINENKENTUCKY70MM</t>
+          <t>GRND7CONTINENTALKENTUCKY</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -12641,13 +13658,23 @@
       <c r="BC107" t="inlineStr">
         <is>
           <t>SALE item ('7.0 only'). No regular equivalent in this tier -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named).</t>
+        </is>
+      </c>
+      <c r="BE107" t="inlineStr">
+        <is>
+          <t>recyYOdijo7wSjDAg</t>
+        </is>
+      </c>
+      <c r="BF107" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>GRNDLVP-0006</t>
+          <t>SPC-GRAN-0011</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -12667,7 +13694,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>GRNDCONTINENMICHIGAN70MM</t>
+          <t>GRND7CONTINENTALMICHIGAN</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -12768,13 +13795,23 @@
       <c r="BC108" t="inlineStr">
         <is>
           <t>SALE item ('7.0 only'). No regular equivalent in this tier -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named).</t>
+        </is>
+      </c>
+      <c r="BE108" t="inlineStr">
+        <is>
+          <t>reciqcd1jZcULQyrj</t>
+        </is>
+      </c>
+      <c r="BF108" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GRNDLVP-0007</t>
+          <t>SPC-GRAN-0012</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -12794,7 +13831,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>GRNDCONTINENNEWJERSEY70MM</t>
+          <t>GRND7CONTINENTALNEWJERSEY</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -12895,13 +13932,23 @@
       <c r="BC109" t="inlineStr">
         <is>
           <t>SALE item ('7.0 only'). No regular equivalent in this tier -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named).</t>
+        </is>
+      </c>
+      <c r="BE109" t="inlineStr">
+        <is>
+          <t>recfuQBPr6rK86r1E</t>
+        </is>
+      </c>
+      <c r="BF109" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>GRNDLVP-0008</t>
+          <t>SPC-GRAN-0013</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -12921,7 +13968,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>GRNDCONTINENNEWYORK70MM</t>
+          <t>GRND7CONTINENTALNEWYORK</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -13022,13 +14069,23 @@
       <c r="BC110" t="inlineStr">
         <is>
           <t>SALE item ('7.0 only'). No regular equivalent in this tier -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named).</t>
+        </is>
+      </c>
+      <c r="BE110" t="inlineStr">
+        <is>
+          <t>recylRp2uAuslvGKT</t>
+        </is>
+      </c>
+      <c r="BF110" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>GRNDLVP-0009</t>
+          <t>SPC-GRAN-0014</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -13048,7 +14105,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>GRNDCONTINENWISCONSIN70MM</t>
+          <t>GRND7CONTINENTALWISCONSIN</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -13149,13 +14206,23 @@
       <c r="BC111" t="inlineStr">
         <is>
           <t>SALE item ('7.0 only'). No regular equivalent in this tier -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named).</t>
+        </is>
+      </c>
+      <c r="BE111" t="inlineStr">
+        <is>
+          <t>reckvSQshct09aUre</t>
+        </is>
+      </c>
+      <c r="BF111" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>GRNDLVP-0010</t>
+          <t>SPC-GRAN-0005</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -13175,7 +14242,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>GRNDCONTINENPENNSYLVANIA60MM</t>
+          <t>GRND7CONTINENTALPENNSYLVANIA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -13273,13 +14340,23 @@
       <c r="BC112" t="inlineStr">
         <is>
           <t>Only non-SALE colour in Continental ('6.0 only'). Composition: 5.0mm SPC + 1.0mm underpad (material not named). See Volume pricing notes for a bulk buyout offer printed on this line.</t>
+        </is>
+      </c>
+      <c r="BE112" t="inlineStr">
+        <is>
+          <t>rechqmOXjzBv2XT0x</t>
+        </is>
+      </c>
+      <c r="BF112" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GRNDLVP-0011</t>
+          <t>SPC-GRAN-0015</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -13299,7 +14376,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>GRNDPACIFICCANTERBURY</t>
+          <t>GRND7PACIFICCANTERBURY</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -13400,13 +14477,23 @@
       <c r="BC113" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. FLAG FOR ALBERT: Pacific collection prints two box sizes (17.72sf/box @ 7"x60"x7mm and 18.91sf/box @ 7"x48"x7mm) at the same price without indicating which colours use which length; defaulted to the 60" length/17.72sf/box for all Pacific colours -- confirm per-colour length with Grandeur. Composition: 5.5mm SPC + 1.5mm underpad (material not named).</t>
+        </is>
+      </c>
+      <c r="BE113" t="inlineStr">
+        <is>
+          <t>rec00Qc64m4JB0T13</t>
+        </is>
+      </c>
+      <c r="BF113" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>GRNDLVP-0012</t>
+          <t>SPC-GRAN-0016</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -13426,7 +14513,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>GRNDPACIFICGOLDENBAY</t>
+          <t>GRND7PACIFICGOLDENBAY</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -13527,13 +14614,23 @@
       <c r="BC114" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. FLAG FOR ALBERT: Pacific collection prints two box sizes (17.72sf/box @ 7"x60"x7mm and 18.91sf/box @ 7"x48"x7mm) at the same price without indicating which colours use which length; defaulted to the 60" length/17.72sf/box for all Pacific colours -- confirm per-colour length with Grandeur. Composition: 5.5mm SPC + 1.5mm underpad (material not named).</t>
+        </is>
+      </c>
+      <c r="BE114" t="inlineStr">
+        <is>
+          <t>reciiK1kWu3uBYLIb</t>
+        </is>
+      </c>
+      <c r="BF114" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>GRNDLVP-0013</t>
+          <t>SPC-GRAN-0017</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -13553,7 +14650,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>GRNDPACIFICQUEENSTOWN</t>
+          <t>GRND7PACIFICQUEENSTOWN</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -13654,13 +14751,23 @@
       <c r="BC115" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. FLAG FOR ALBERT: Pacific collection prints two box sizes (17.72sf/box @ 7"x60"x7mm and 18.91sf/box @ 7"x48"x7mm) at the same price without indicating which colours use which length; defaulted to the 60" length/17.72sf/box for all Pacific colours -- confirm per-colour length with Grandeur. Composition: 5.5mm SPC + 1.5mm underpad (material not named).</t>
+        </is>
+      </c>
+      <c r="BE115" t="inlineStr">
+        <is>
+          <t>reczWaFbpwD9vBNL2</t>
+        </is>
+      </c>
+      <c r="BF115" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>GRNDLVP-0014</t>
+          <t>SPC-GRAN-0018</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -13680,7 +14787,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>GRNDPACIFICWELLINGTON</t>
+          <t>GRND7PACIFICWELLINGTON</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -13786,13 +14893,23 @@
       <c r="BC116" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. FLAG FOR ALBERT: Pacific collection prints two box sizes (17.72sf/box @ 7"x60"x7mm and 18.91sf/box @ 7"x48"x7mm) at the same price without indicating which colours use which length; defaulted to the 60" length/17.72sf/box for all Pacific colours -- confirm per-colour length with Grandeur. Composition: 5.5mm SPC + 1.5mm underpad (material not named). Marked Low Stock.</t>
+        </is>
+      </c>
+      <c r="BE116" t="inlineStr">
+        <is>
+          <t>rec4ShCF5XTP5huyT</t>
+        </is>
+      </c>
+      <c r="BF116" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>GRNDLVP-0015</t>
+          <t>SPC-GRAN-0019</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -13817,7 +14934,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>GRNDPACIFIC880062</t>
+          <t>GRND7PACIFIC880062</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -13918,13 +15035,23 @@
       <c r="BC117" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. FLAG FOR ALBERT: Pacific collection prints two box sizes (17.72sf/box @ 7"x60"x7mm and 18.91sf/box @ 7"x48"x7mm) at the same price without indicating which colours use which length; defaulted to the 60" length/17.72sf/box for all Pacific colours -- confirm per-colour length with Grandeur. Composition: 5.5mm SPC + 1.5mm underpad (material not named). Colour name not provided -- product identified only by code '88006-2'; used as colour placeholder.</t>
+        </is>
+      </c>
+      <c r="BE117" t="inlineStr">
+        <is>
+          <t>recbj5Mgifa59GstW</t>
+        </is>
+      </c>
+      <c r="BF117" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>GRNDLVP-0016</t>
+          <t>SPC-GRAN-0020</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13944,7 +15071,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>GRNDANCHOR7BATTERYPOINT</t>
+          <t>GRND7ANCHOR7BATTERYPOINT</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -14045,13 +15172,23 @@
       <c r="BC118" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named). *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE118" t="inlineStr">
+        <is>
+          <t>recFz1qz2mRaVij6U</t>
+        </is>
+      </c>
+      <c r="BF118" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>GRNDLVP-0017</t>
+          <t>SPC-GRAN-0021</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -14071,7 +15208,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>GRNDANCHOR7NORTHHEAD</t>
+          <t>GRND7ANCHOR7NORTHHEAD</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -14172,13 +15309,23 @@
       <c r="BC119" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named). *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE119" t="inlineStr">
+        <is>
+          <t>recmrIhE42brJel2B</t>
+        </is>
+      </c>
+      <c r="BF119" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>GRNDLVP-0018</t>
+          <t>SPC-GRAN-0022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -14198,7 +15345,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>GRNDANCHOR7OAKISLAND</t>
+          <t>GRND7ANCHOR7OAKISLAND</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -14299,13 +15446,23 @@
       <c r="BC120" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named). *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE120" t="inlineStr">
+        <is>
+          <t>recvqPnb8yTI0BfrM</t>
+        </is>
+      </c>
+      <c r="BF120" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>GRNDLVP-0019</t>
+          <t>SPC-GRAN-0023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -14325,7 +15482,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>GRNDANCHOR7PEGGYSCOVE</t>
+          <t>GRND7ANCHOR7PEGGYSCOVE</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -14426,13 +15583,23 @@
       <c r="BC121" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named). *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE121" t="inlineStr">
+        <is>
+          <t>recNR5bTsYqU3JFnv</t>
+        </is>
+      </c>
+      <c r="BF121" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GRNDLVP-0020</t>
+          <t>SPC-GRAN-0024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -14452,7 +15619,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>GRNDANCHOR7POINTREYES</t>
+          <t>GRND7ANCHOR7POINTREYES</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -14553,13 +15720,23 @@
       <c r="BC122" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named). *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE122" t="inlineStr">
+        <is>
+          <t>recVONp06BMwvPVGh</t>
+        </is>
+      </c>
+      <c r="BF122" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GRNDLVP-0021</t>
+          <t>SPC-GRAN-0025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -14579,7 +15756,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>GRNDANCHOR7SAMBRO</t>
+          <t>GRND7ANCHOR7SAMBRO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -14680,13 +15857,23 @@
       <c r="BC123" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named). *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE123" t="inlineStr">
+        <is>
+          <t>reclcUhm8RJsjN6dN</t>
+        </is>
+      </c>
+      <c r="BF123" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GRNDLVP-0022</t>
+          <t>SPC-GRAN-0026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -14706,7 +15893,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>GRNDANCHOR7WINDPOINT</t>
+          <t>GRND7ANCHOR7WINDPOINT</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -14807,13 +15994,23 @@
       <c r="BC124" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named). *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE124" t="inlineStr">
+        <is>
+          <t>recJ5HdyzhknYtZaH</t>
+        </is>
+      </c>
+      <c r="BF124" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GRNDLVP-0023</t>
+          <t>SPC-GRAN-0027</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -14833,7 +16030,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>GRNDWONDER7ALEXANDRIA</t>
+          <t>GRND7WONDER7ALEXANDRIA</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -14934,13 +16131,23 @@
       <c r="BC125" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named). *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE125" t="inlineStr">
+        <is>
+          <t>recC3pQSi0k7U46H1</t>
+        </is>
+      </c>
+      <c r="BF125" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GRNDLVP-0024</t>
+          <t>SPC-GRAN-0028</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -14960,7 +16167,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>GRNDWONDER7BABYLON</t>
+          <t>GRND7WONDER7BABYLON</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -15061,13 +16268,23 @@
       <c r="BC126" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named). *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE126" t="inlineStr">
+        <is>
+          <t>recVzN0jtL0m8ysNf</t>
+        </is>
+      </c>
+      <c r="BF126" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GRNDLVP-0025</t>
+          <t>SPC-GRAN-0029</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -15087,7 +16304,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>GRNDWONDER7COLISEUM</t>
+          <t>GRND7WONDER7COLISEUM</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -15188,13 +16405,23 @@
       <c r="BC127" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named). *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE127" t="inlineStr">
+        <is>
+          <t>recDaWz18B3lGR8fN</t>
+        </is>
+      </c>
+      <c r="BF127" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GRNDLVP-0026</t>
+          <t>SPC-GRAN-0030</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -15214,7 +16441,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>GRNDWONDER7GIZA</t>
+          <t>GRND7WONDER7GIZA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -15315,13 +16542,23 @@
       <c r="BC128" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named). *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE128" t="inlineStr">
+        <is>
+          <t>recCxmoCulKie7E4n</t>
+        </is>
+      </c>
+      <c r="BF128" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GRNDLVP-0027</t>
+          <t>SPC-GRAN-0031</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -15341,7 +16578,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>GRNDWONDER7OLYMPIA</t>
+          <t>GRND7WONDER7OLYMPIA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -15442,13 +16679,23 @@
       <c r="BC129" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named). *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE129" t="inlineStr">
+        <is>
+          <t>recEtSpI6rr4dTP3C</t>
+        </is>
+      </c>
+      <c r="BF129" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GRNDLVP-0028</t>
+          <t>SPC-GRAN-0032</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -15468,7 +16715,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>GRNDWONDER7PETRA</t>
+          <t>GRND7WONDER7PETRA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -15569,13 +16816,23 @@
       <c r="BC130" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named). *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE130" t="inlineStr">
+        <is>
+          <t>recO6yaDrmfGi02qw</t>
+        </is>
+      </c>
+      <c r="BF130" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>GRNDLVP-0029</t>
+          <t>SPC-GRAN-0033</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -15595,7 +16852,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>GRNDWONDER7RHODES</t>
+          <t>GRND7WONDER7RHODES</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -15696,13 +16953,23 @@
       <c r="BC131" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 5.5mm SPC + 1.5mm underpad (material not named). *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE131" t="inlineStr">
+        <is>
+          <t>reclvKtnbxRrxGjkh</t>
+        </is>
+      </c>
+      <c r="BF131" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>GRNDLVP-0030</t>
+          <t>LVP-GRAN-0037</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -15722,7 +16989,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>GRNDINOV8COVEISLAND</t>
+          <t>GRND7INOV8COVEISLAND</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -15824,14 +17091,19 @@
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>Listed as 'Stone Plastic Composite Vinyl' but composition states 'Engineered Vinyl' core (6.5mm + 1.5mm underpad, material not named). Material type defaulted to SPC core per the documented Grandeur/LS ambiguous-core convention. *3in1 Matching Tread Package Available.</t>
+          <t>NEW PRODUCT — not present in the live Master Flooring Catalogue on 2026-09-03. SKU LVP-GRAN-0037 assigned continuing the live LVP-GRAN sequence. Note: the live base also holds legacy SPC-GRAN-/WPC-GRAN- prefixed vinyl; per the current schema rule new vinyl takes the LVP/LVT prefix, so this supplier's vinyl SKUs now mix both conventions. | Listed as 'Stone Plastic Composite Vinyl' but composition states 'Engineered Vinyl' core (6.5mm + 1.5mm underpad, material not named). Material type defaulted to SPC core per the documented Grandeur/LS ambiguous-core convention. *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BF132" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>GRNDLVP-0031</t>
+          <t>SPC-GRAN-0034</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -15851,7 +17123,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>GRNDINOV8FLOWERPOTISLAND</t>
+          <t>GRND7INOV8FLOWERPOTISLAND</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -15954,13 +17226,23 @@
       <c r="BC133" t="inlineStr">
         <is>
           <t>Listed as 'Stone Plastic Composite Vinyl' but composition states 'Engineered Vinyl' core (6.5mm + 1.5mm underpad, material not named). Material type defaulted to SPC core per the documented Grandeur/LS ambiguous-core convention. *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE133" t="inlineStr">
+        <is>
+          <t>recxvcVRcTZ0w4CvC</t>
+        </is>
+      </c>
+      <c r="BF133" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>GRNDLVP-0032</t>
+          <t>SPC-GRAN-0035</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -15980,7 +17262,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>GRNDINOV8LIONSHEAD</t>
+          <t>GRND7INOV8LIONSHEAD</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -16083,13 +17365,23 @@
       <c r="BC134" t="inlineStr">
         <is>
           <t>Listed as 'Stone Plastic Composite Vinyl' but composition states 'Engineered Vinyl' core (6.5mm + 1.5mm underpad, material not named). Material type defaulted to SPC core per the documented Grandeur/LS ambiguous-core convention. *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE134" t="inlineStr">
+        <is>
+          <t>recvU9Vc3x2OiJcqr</t>
+        </is>
+      </c>
+      <c r="BF134" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>GRNDLVP-0033</t>
+          <t>SPC-GRAN-0036</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -16109,7 +17401,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>GRNDINOV8MANITOULIN</t>
+          <t>GRND7INOV8MANITOULIN</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -16212,13 +17504,23 @@
       <c r="BC135" t="inlineStr">
         <is>
           <t>Listed as 'Stone Plastic Composite Vinyl' but composition states 'Engineered Vinyl' core (6.5mm + 1.5mm underpad, material not named). Material type defaulted to SPC core per the documented Grandeur/LS ambiguous-core convention. *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE135" t="inlineStr">
+        <is>
+          <t>recU13NQTpGUA9Gem</t>
+        </is>
+      </c>
+      <c r="BF135" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>GRNDLVP-0034</t>
+          <t>SPC-GRAN-0037</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -16238,7 +17540,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>GRNDINOV8MERMAIDSCOVE</t>
+          <t>GRND7INOV8MERMAIDSCOVE</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -16341,13 +17643,23 @@
       <c r="BC136" t="inlineStr">
         <is>
           <t>Listed as 'Stone Plastic Composite Vinyl' but composition states 'Engineered Vinyl' core (6.5mm + 1.5mm underpad, material not named). Material type defaulted to SPC core per the documented Grandeur/LS ambiguous-core convention. *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE136" t="inlineStr">
+        <is>
+          <t>recA91war83tQQKbe</t>
+        </is>
+      </c>
+      <c r="BF136" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>GRNDLVP-0035</t>
+          <t>SPC-GRAN-0038</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -16367,7 +17679,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>GRNDINOV8PENINSULA</t>
+          <t>GRND7INOV8PENINSULA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -16470,13 +17782,23 @@
       <c r="BC137" t="inlineStr">
         <is>
           <t>Listed as 'Stone Plastic Composite Vinyl' but composition states 'Engineered Vinyl' core (6.5mm + 1.5mm underpad, material not named). Material type defaulted to SPC core per the documented Grandeur/LS ambiguous-core convention. *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE137" t="inlineStr">
+        <is>
+          <t>recKM0qQWU5KcGIfj</t>
+        </is>
+      </c>
+      <c r="BF137" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>GRNDLVP-0036</t>
+          <t>LVP-GRAN-0038</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -16496,7 +17818,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>GRNDINOV8SAUBLEBEACH</t>
+          <t>GRND7INOV8SAUBLEBEACH</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -16598,14 +17920,19 @@
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>Listed as 'Stone Plastic Composite Vinyl' but composition states 'Engineered Vinyl' core (6.5mm + 1.5mm underpad, material not named). Material type defaulted to SPC core per the documented Grandeur/LS ambiguous-core convention. *3in1 Matching Tread Package Available.</t>
+          <t>NEW PRODUCT — not present in the live Master Flooring Catalogue on 2026-09-03. SKU LVP-GRAN-0038 assigned continuing the live LVP-GRAN sequence. Note: the live base also holds legacy SPC-GRAN-/WPC-GRAN- prefixed vinyl; per the current schema rule new vinyl takes the LVP/LVT prefix, so this supplier's vinyl SKUs now mix both conventions. | Listed as 'Stone Plastic Composite Vinyl' but composition states 'Engineered Vinyl' core (6.5mm + 1.5mm underpad, material not named). Material type defaulted to SPC core per the documented Grandeur/LS ambiguous-core convention. *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BF138" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>GRNDLVP-0037</t>
+          <t>SPC-GRAN-0039</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -16625,7 +17952,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>GRNDINOV8TOBERMORY</t>
+          <t>GRND7INOV8TOBERMORY</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -16728,13 +18055,23 @@
       <c r="BC139" t="inlineStr">
         <is>
           <t>Listed as 'Stone Plastic Composite Vinyl' but composition states 'Engineered Vinyl' core (6.5mm + 1.5mm underpad, material not named). Material type defaulted to SPC core per the documented Grandeur/LS ambiguous-core convention. *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE139" t="inlineStr">
+        <is>
+          <t>recMxdq9bbPsfEwI8</t>
+        </is>
+      </c>
+      <c r="BF139" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>GRNDLVP-0038</t>
+          <t>SPC-GRAN-0040</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -16754,7 +18091,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>GRNDDESIGNERALEXANDRIAHB</t>
+          <t>GRND5DESIGNERALEXANDRIAHB</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -16852,13 +18189,23 @@
       <c r="BC140" t="inlineStr">
         <is>
           <t>Composition: 5.5mm SPC + 1.5mm underpad (material not named). *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE140" t="inlineStr">
+        <is>
+          <t>recxOnanu2CHdNU92</t>
+        </is>
+      </c>
+      <c r="BF140" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>GRNDLVP-0039</t>
+          <t>SPC-GRAN-0041</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -16878,7 +18225,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>GRNDDESIGNERNORTHHEADHB</t>
+          <t>GRND5DESIGNERNORTHHEADHB</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -16976,13 +18323,23 @@
       <c r="BC141" t="inlineStr">
         <is>
           <t>Composition: 5.5mm SPC + 1.5mm underpad (material not named). *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE141" t="inlineStr">
+        <is>
+          <t>recxpYaOxL9PKBQZH</t>
+        </is>
+      </c>
+      <c r="BF141" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>GRNDLVP-0040</t>
+          <t>SPC-GRAN-0042</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -17002,7 +18359,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>GRNDDESIGNERRHODESHB</t>
+          <t>GRND5DESIGNERRHODESHB</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -17100,13 +18457,23 @@
       <c r="BC142" t="inlineStr">
         <is>
           <t>Composition: 5.5mm SPC + 1.5mm underpad (material not named). *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE142" t="inlineStr">
+        <is>
+          <t>recITHU2LntCuZEiR</t>
+        </is>
+      </c>
+      <c r="BF142" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>GRNDLVP-0041</t>
+          <t>SPC-GRAN-0043</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -17126,7 +18493,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>GRNDDESIGNERRICELAKEHB</t>
+          <t>GRND5DESIGNERRICELAKEHB</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -17224,13 +18591,23 @@
       <c r="BC143" t="inlineStr">
         <is>
           <t>Composition: 5.5mm SPC + 1.5mm underpad (material not named). *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE143" t="inlineStr">
+        <is>
+          <t>recJHoLiF7devVscq</t>
+        </is>
+      </c>
+      <c r="BF143" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>GRNDLVP-0042</t>
+          <t>SPC-GRAN-0044</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -17250,7 +18627,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>GRNDDESIGNERSAMBROHB</t>
+          <t>GRND5DESIGNERSAMBROHB</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -17348,13 +18725,23 @@
       <c r="BC144" t="inlineStr">
         <is>
           <t>Composition: 5.5mm SPC + 1.5mm underpad (material not named). *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE144" t="inlineStr">
+        <is>
+          <t>rec47JplaDywtVU9O</t>
+        </is>
+      </c>
+      <c r="BF144" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>GRNDLVP-0043</t>
+          <t>SPC-GRAN-0045</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -17374,7 +18761,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>GRNDDESIGNERWINDPOINTHB</t>
+          <t>GRND5DESIGNERWINDPOINTHB</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -17472,13 +18859,23 @@
       <c r="BC145" t="inlineStr">
         <is>
           <t>Composition: 5.5mm SPC + 1.5mm underpad (material not named). *3in1 Matching Tread Package Available.</t>
+        </is>
+      </c>
+      <c r="BE145" t="inlineStr">
+        <is>
+          <t>recU6UY3cxOWks21O</t>
+        </is>
+      </c>
+      <c r="BF145" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>GRNDLVP-0044</t>
+          <t>WPC-GRAN-0001</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -17498,7 +18895,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>GRNDBLISSAUGUSTDUSK</t>
+          <t>GRND9BLISSAUGUSTDUSK</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -17591,13 +18988,23 @@
       <c r="AW146" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BE146" t="inlineStr">
+        <is>
+          <t>rec8o5Mn4vXRXTNRf</t>
+        </is>
+      </c>
+      <c r="BF146" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>GRNDLVP-0045</t>
+          <t>WPC-GRAN-0002</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -17617,7 +19024,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>GRNDBLISSCAMPFIRE</t>
+          <t>GRND9BLISSCAMPFIRE</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -17710,13 +19117,23 @@
       <c r="AW147" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BE147" t="inlineStr">
+        <is>
+          <t>recQlaLqXrmoTi5TB</t>
+        </is>
+      </c>
+      <c r="BF147" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>GRNDLVP-0046</t>
+          <t>WPC-GRAN-0003</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -17736,7 +19153,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>GRNDBLISSGAZEBO</t>
+          <t>GRND9BLISSGAZEBO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -17829,13 +19246,23 @@
       <c r="AW148" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BE148" t="inlineStr">
+        <is>
+          <t>recw4Pms75zWKmI7L</t>
+        </is>
+      </c>
+      <c r="BF148" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>GRNDLVP-0047</t>
+          <t>WPC-GRAN-0004</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -17855,7 +19282,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>GRNDBLISSHIKINGTRAIL</t>
+          <t>GRND9BLISSHIKINGTRAIL</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -17948,13 +19375,23 @@
       <c r="AW149" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BE149" t="inlineStr">
+        <is>
+          <t>recIzsrlBsr2AcQ8Q</t>
+        </is>
+      </c>
+      <c r="BF149" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>GRNDLVP-0048</t>
+          <t>WPC-GRAN-0005</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -17974,7 +19411,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>GRNDBLISSMORNINGDEW</t>
+          <t>GRND9BLISSMORNINGDEW</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -18067,13 +19504,23 @@
       <c r="AW150" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BE150" t="inlineStr">
+        <is>
+          <t>reccUpBuMvlcXpMgF</t>
+        </is>
+      </c>
+      <c r="BF150" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>GRNDLVP-0049</t>
+          <t>WPC-GRAN-0006</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -18093,7 +19540,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>GRNDBLISSSTARLIGHT</t>
+          <t>GRND9BLISSSTARLIGHT</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -18186,13 +19633,23 @@
       <c r="AW151" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BE151" t="inlineStr">
+        <is>
+          <t>recLLK1mQHb2sANAF</t>
+        </is>
+      </c>
+      <c r="BF151" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>GRNDLVP-0050</t>
+          <t>WPC-GRAN-0007</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -18212,7 +19669,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>GRNDBLISSSEABREEZE</t>
+          <t>GRND9BLISSSEABREEZE</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -18305,13 +19762,23 @@
       <c r="AW152" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BE152" t="inlineStr">
+        <is>
+          <t>rechZGJvASvnajmZV</t>
+        </is>
+      </c>
+      <c r="BF152" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>GRNDLVP-0051</t>
+          <t>WPC-GRAN-0008</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -18331,7 +19798,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>GRNDBLISSSUMMERSHADE</t>
+          <t>GRND9BLISSSUMMERSHADE</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -18424,13 +19891,23 @@
       <c r="AW153" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BE153" t="inlineStr">
+        <is>
+          <t>recFKC1rizNol3yrH</t>
+        </is>
+      </c>
+      <c r="BF153" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>GRNDLVP-0052</t>
+          <t>WPC-GRAN-0009</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -18450,7 +19927,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>GRNDBLISSTREEHOUSE</t>
+          <t>GRND9BLISSTREEHOUSE</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -18543,13 +20020,23 @@
       <c r="AW154" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BE154" t="inlineStr">
+        <is>
+          <t>reccAKVf30QaaHPii</t>
+        </is>
+      </c>
+      <c r="BF154" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>GRNDLVP-0053</t>
+          <t>WPC-GRAN-0010</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -18569,7 +20056,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>GRNDBLISSWOODLAND</t>
+          <t>GRND9BLISSWOODLAND</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -18662,13 +20149,23 @@
       <c r="AW155" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BE155" t="inlineStr">
+        <is>
+          <t>recTYdjQoDCArbjpe</t>
+        </is>
+      </c>
+      <c r="BF155" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>GRNDLVP-0054</t>
+          <t>LVP-GRAN-0039</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -18688,7 +20185,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>GRNDBEACONCAVENDISH</t>
+          <t>GRND7BEACONCAVENDISH</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -18791,13 +20288,23 @@
       <c r="AW156" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr">
+        <is>
+          <t>NEW PRODUCT — not present in the live Master Flooring Catalogue on 2026-09-03. SKU LVP-GRAN-0039 assigned continuing the live LVP-GRAN sequence. Note: the live base also holds legacy SPC-GRAN-/WPC-GRAN- prefixed vinyl; per the current schema rule new vinyl takes the LVP/LVT prefix, so this supplier's vinyl SKUs now mix both conventions.</t>
+        </is>
+      </c>
+      <c r="BF156" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>GRNDLVP-0055</t>
+          <t>LVP-GRAN-0040</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -18817,7 +20324,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>GRNDBEACONHOPEWELL</t>
+          <t>GRND7BEACONHOPEWELL</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -18920,13 +20427,23 @@
       <c r="AW157" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
+        <is>
+          <t>NEW PRODUCT — not present in the live Master Flooring Catalogue on 2026-09-03. SKU LVP-GRAN-0040 assigned continuing the live LVP-GRAN sequence. Note: the live base also holds legacy SPC-GRAN-/WPC-GRAN- prefixed vinyl; per the current schema rule new vinyl takes the LVP/LVT prefix, so this supplier's vinyl SKUs now mix both conventions.</t>
+        </is>
+      </c>
+      <c r="BF157" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>GRNDLVP-0056</t>
+          <t>LVP-GRAN-0041</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -18946,7 +20463,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>GRNDBEACONLIGHTHOUSE</t>
+          <t>GRND7BEACONLIGHTHOUSE</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -19049,13 +20566,23 @@
       <c r="AW158" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>NEW PRODUCT — not present in the live Master Flooring Catalogue on 2026-09-03. SKU LVP-GRAN-0041 assigned continuing the live LVP-GRAN sequence. Note: the live base also holds legacy SPC-GRAN-/WPC-GRAN- prefixed vinyl; per the current schema rule new vinyl takes the LVP/LVT prefix, so this supplier's vinyl SKUs now mix both conventions.</t>
+        </is>
+      </c>
+      <c r="BF158" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>GRNDLVP-0057</t>
+          <t>LVP-GRAN-0042</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -19075,7 +20602,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>GRNDBEACONLUNENBURG</t>
+          <t>GRND7BEACONLUNENBURG</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -19178,13 +20705,23 @@
       <c r="AW159" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
+        <is>
+          <t>NEW PRODUCT — not present in the live Master Flooring Catalogue on 2026-09-03. SKU LVP-GRAN-0042 assigned continuing the live LVP-GRAN sequence. Note: the live base also holds legacy SPC-GRAN-/WPC-GRAN- prefixed vinyl; per the current schema rule new vinyl takes the LVP/LVT prefix, so this supplier's vinyl SKUs now mix both conventions.</t>
+        </is>
+      </c>
+      <c r="BF159" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>GRNDLVP-0058</t>
+          <t>LVP-GRAN-0043</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -19204,7 +20741,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>GRNDBEACONSEAGLASS</t>
+          <t>GRND7BEACONSEAGLASS</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -19307,13 +20844,23 @@
       <c r="AW160" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>NEW PRODUCT — not present in the live Master Flooring Catalogue on 2026-09-03. SKU LVP-GRAN-0043 assigned continuing the live LVP-GRAN sequence. Note: the live base also holds legacy SPC-GRAN-/WPC-GRAN- prefixed vinyl; per the current schema rule new vinyl takes the LVP/LVT prefix, so this supplier's vinyl SKUs now mix both conventions.</t>
+        </is>
+      </c>
+      <c r="BF160" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>GRNDLVP-0059</t>
+          <t>LVP-GRAN-0044</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -19333,7 +20880,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>GRNDBEACONSINGINGSANDS</t>
+          <t>GRND7BEACONSINGINGSANDS</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -19436,13 +20983,23 @@
       <c r="AW161" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
+        <is>
+          <t>NEW PRODUCT — not present in the live Master Flooring Catalogue on 2026-09-03. SKU LVP-GRAN-0044 assigned continuing the live LVP-GRAN sequence. Note: the live base also holds legacy SPC-GRAN-/WPC-GRAN- prefixed vinyl; per the current schema rule new vinyl takes the LVP/LVT prefix, so this supplier's vinyl SKUs now mix both conventions.</t>
+        </is>
+      </c>
+      <c r="BF161" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>GRNDLVP-0060</t>
+          <t>WPC-GRAN-0011</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -19462,7 +21019,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>GRNDSUPREMEXAUTUMNBLAZE</t>
+          <t>GRND9SUPREMEXAUTUMNBLAZE</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -19555,13 +21112,23 @@
       <c r="AW162" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BE162" t="inlineStr">
+        <is>
+          <t>recJkbO8jFw9fYc04</t>
+        </is>
+      </c>
+      <c r="BF162" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>GRNDLVP-0061</t>
+          <t>WPC-GRAN-0012</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -19581,7 +21148,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>GRNDSUPREMEXARCTICWHISPER</t>
+          <t>GRND9SUPREMEXARCTICWHISPER</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -19674,13 +21241,23 @@
       <c r="AW163" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BE163" t="inlineStr">
+        <is>
+          <t>rec0sVrmvPxCUzrfy</t>
+        </is>
+      </c>
+      <c r="BF163" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>GRNDLVP-0062</t>
+          <t>WPC-GRAN-0013</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -19700,7 +21277,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>GRNDSUPREMEXBUTTERCUP</t>
+          <t>GRND9SUPREMEXBUTTERCUP</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -19793,13 +21370,23 @@
       <c r="AW164" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BE164" t="inlineStr">
+        <is>
+          <t>rectao3BcElSfydMc</t>
+        </is>
+      </c>
+      <c r="BF164" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>GRNDLVP-0063</t>
+          <t>WPC-GRAN-0014</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -19819,7 +21406,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>GRNDSUPREMEXCITRUSLEAF</t>
+          <t>GRND9SUPREMEXCITRUSLEAF</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -19912,13 +21499,23 @@
       <c r="AW165" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BE165" t="inlineStr">
+        <is>
+          <t>rec2kipBkHHQxDqiD</t>
+        </is>
+      </c>
+      <c r="BF165" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>GRNDLVP-0064</t>
+          <t>WPC-GRAN-0016</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -19938,7 +21535,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>GRNDSUPREMEXEBONYECLIPSE</t>
+          <t>GRND9SUPREMEXEBONYECLIPSE</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -20031,13 +21628,23 @@
       <c r="AW166" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BE166" t="inlineStr">
+        <is>
+          <t>recvUIicFLX98mx4H</t>
+        </is>
+      </c>
+      <c r="BF166" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>GRNDLVP-0065</t>
+          <t>WPC-GRAN-0017</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -20057,7 +21664,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>GRNDSUPREMEXLEMONZEST</t>
+          <t>GRND9SUPREMEXLEMONZEST</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -20150,13 +21757,23 @@
       <c r="AW167" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BE167" t="inlineStr">
+        <is>
+          <t>recKX7qKX35XULr1S</t>
+        </is>
+      </c>
+      <c r="BF167" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>GRNDLVP-0066</t>
+          <t>WPC-GRAN-0019</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -20176,7 +21793,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>GRNDSUPREMEXSUNBEAM</t>
+          <t>GRND9SUPREMEXSUNBEAM</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -20269,13 +21886,23 @@
       <c r="AW168" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BE168" t="inlineStr">
+        <is>
+          <t>recyaBxIDI6tCQ2yL</t>
+        </is>
+      </c>
+      <c r="BF168" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>GRNDLVP-0067</t>
+          <t>WPC-GRAN-0020</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -20295,7 +21922,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>GRNDSUPREMEXTOFFEEAPPLE</t>
+          <t>GRND9SUPREMEXTOFFEEAPPLE</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -20388,13 +22015,23 @@
       <c r="AW169" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="BE169" t="inlineStr">
+        <is>
+          <t>rec0qYvvbR6abpuxg</t>
+        </is>
+      </c>
+      <c r="BF169" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>GRNDLVP-0068</t>
+          <t>LVP-GRAN-0001</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -20414,7 +22051,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>GRNDESSENTIAALGONQUIN</t>
+          <t>GRND7ESSENTIALALGONQUIN</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -20506,13 +22143,23 @@
       <c r="BC170" t="inlineStr">
         <is>
           <t>Material type set to 'Dry-back vinyl' per the Woden-precedent value for dry-back/glue-down vinyl -- Grandeur subsection doesn't explicitly define this Material type; confirm the value is acceptable in the live schema. Marked Low Stock.</t>
+        </is>
+      </c>
+      <c r="BE170" t="inlineStr">
+        <is>
+          <t>rec3jappVHVdnycoI</t>
+        </is>
+      </c>
+      <c r="BF170" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>GRNDLVP-0069</t>
+          <t>LVP-GRAN-0003</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -20532,7 +22179,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>GRNDESSENTIAGEORGIANBAY</t>
+          <t>GRND7ESSENTIALGEORGIANBAY</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -20619,13 +22266,23 @@
       <c r="BC171" t="inlineStr">
         <is>
           <t>Material type set to 'Dry-back vinyl' per the Woden-precedent value for dry-back/glue-down vinyl -- Grandeur subsection doesn't explicitly define this Material type; confirm the value is acceptable in the live schema.</t>
+        </is>
+      </c>
+      <c r="BE171" t="inlineStr">
+        <is>
+          <t>rec8Hvo3iQM1RvBql</t>
+        </is>
+      </c>
+      <c r="BF171" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>GRNDLVP-0070</t>
+          <t>LVP-GRAN-0004</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -20645,7 +22302,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>GRNDESSENTIAKAWARTHA</t>
+          <t>GRND7ESSENTIALKAWARTHA</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -20732,13 +22389,23 @@
       <c r="BC172" t="inlineStr">
         <is>
           <t>Material type set to 'Dry-back vinyl' per the Woden-precedent value for dry-back/glue-down vinyl -- Grandeur subsection doesn't explicitly define this Material type; confirm the value is acceptable in the live schema.</t>
+        </is>
+      </c>
+      <c r="BE172" t="inlineStr">
+        <is>
+          <t>recKxfnH3TM8baOJo</t>
+        </is>
+      </c>
+      <c r="BF172" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>GRNDLVP-0071</t>
+          <t>LVP-GRAN-0005</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -20758,7 +22425,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>GRNDESSENTIALAKESIMCOE</t>
+          <t>GRND7ESSENTIALLAKESIMCOE</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -20845,13 +22512,23 @@
       <c r="BC173" t="inlineStr">
         <is>
           <t>Material type set to 'Dry-back vinyl' per the Woden-precedent value for dry-back/glue-down vinyl -- Grandeur subsection doesn't explicitly define this Material type; confirm the value is acceptable in the live schema.</t>
+        </is>
+      </c>
+      <c r="BE173" t="inlineStr">
+        <is>
+          <t>recyqvpSUSmV6J1DO</t>
+        </is>
+      </c>
+      <c r="BF173" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>GRNDLVP-0072</t>
+          <t>LVP-GRAN-0006</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -20871,7 +22548,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>GRNDESSENTIAMUSKOKA</t>
+          <t>GRND7ESSENTIALMUSKOKA</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -20958,13 +22635,23 @@
       <c r="BC174" t="inlineStr">
         <is>
           <t>Material type set to 'Dry-back vinyl' per the Woden-precedent value for dry-back/glue-down vinyl -- Grandeur subsection doesn't explicitly define this Material type; confirm the value is acceptable in the live schema.</t>
+        </is>
+      </c>
+      <c r="BE174" t="inlineStr">
+        <is>
+          <t>recKoS6qTpmIuP40v</t>
+        </is>
+      </c>
+      <c r="BF174" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>GRNDLVP-0073</t>
+          <t>LVP-GRAN-0007</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -20984,7 +22671,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>GRNDESSENTIASANDBANKS</t>
+          <t>GRND7ESSENTIALSANDBANKS</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -21071,13 +22758,23 @@
       <c r="BC175" t="inlineStr">
         <is>
           <t>Material type set to 'Dry-back vinyl' per the Woden-precedent value for dry-back/glue-down vinyl -- Grandeur subsection doesn't explicitly define this Material type; confirm the value is acceptable in the live schema.</t>
+        </is>
+      </c>
+      <c r="BE175" t="inlineStr">
+        <is>
+          <t>reccTohivsG8UOfhR</t>
+        </is>
+      </c>
+      <c r="BF175" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>GRNDLVT-0001</t>
+          <t>LVP-GRAN-0008</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -21097,7 +22794,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>GRNDESSENTIAFLAGSTONE</t>
+          <t>GRND24ESSENTIALFLAGSTONE</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -21184,13 +22881,23 @@
       <c r="BC176" t="inlineStr">
         <is>
           <t>24"x24" tile-format dry-back vinyl -&gt; Category=LVT. Material type set to 'Dry-back vinyl' per the Woden-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE176" t="inlineStr">
+        <is>
+          <t>recH4l1uM1IpipeK0</t>
+        </is>
+      </c>
+      <c r="BF176" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>GRNDLVT-0002</t>
+          <t>LVP-GRAN-0009</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -21210,7 +22917,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>GRNDESSENTIAHEARTHSTONE</t>
+          <t>GRND24ESSENTIALHEARTHSTONE</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -21297,13 +23004,23 @@
       <c r="BC177" t="inlineStr">
         <is>
           <t>24"x24" tile-format dry-back vinyl -&gt; Category=LVT. Material type set to 'Dry-back vinyl' per the Woden-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE177" t="inlineStr">
+        <is>
+          <t>recmgj2QXGFoMStkw</t>
+        </is>
+      </c>
+      <c r="BF177" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>GRNDLVT-0003</t>
+          <t>LVP-GRAN-0010</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -21323,7 +23040,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>GRNDESSENTIATOUCHSTONE</t>
+          <t>GRND24ESSENTIALTOUCHSTONE</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -21410,13 +23127,23 @@
       <c r="BC178" t="inlineStr">
         <is>
           <t>24"x24" tile-format dry-back vinyl -&gt; Category=LVT. Material type set to 'Dry-back vinyl' per the Woden-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE178" t="inlineStr">
+        <is>
+          <t>recmZ50VNRUkOwsyj</t>
+        </is>
+      </c>
+      <c r="BF178" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>GRNDLVP-0074</t>
+          <t>LVP-GRAN-0011</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -21436,7 +23163,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>GRNDENTREPRECANVASLIGHT</t>
+          <t>GRND7ENTREPRENEURCANVASLIGHT</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -21531,13 +23258,23 @@
       <c r="BC179" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Glassfibre core, Made in Korea. Material type set to 'Dry-back vinyl' per the Woden-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE179" t="inlineStr">
+        <is>
+          <t>reckBgUB2MUJ565z7</t>
+        </is>
+      </c>
+      <c r="BF179" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>GRNDLVP-0075</t>
+          <t>LVP-GRAN-0012</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -21557,7 +23294,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>GRNDENTREPRECHROMADRIFT</t>
+          <t>GRND7ENTREPRENEURCHROMADRIFT</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -21652,13 +23389,23 @@
       <c r="BC180" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Glassfibre core, Made in Korea. Material type set to 'Dry-back vinyl' per the Woden-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE180" t="inlineStr">
+        <is>
+          <t>recfhg7wmcuYxN90w</t>
+        </is>
+      </c>
+      <c r="BF180" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>GRNDLVP-0076</t>
+          <t>LVP-GRAN-0013</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -21678,7 +23425,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>GRNDENTREPREFEATHERGRASS</t>
+          <t>GRND7ENTREPRENEURFEATHERGRASS</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -21773,13 +23520,23 @@
       <c r="BC181" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Glassfibre core, Made in Korea. Material type set to 'Dry-back vinyl' per the Woden-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE181" t="inlineStr">
+        <is>
+          <t>recxTuhw5xZNin11E</t>
+        </is>
+      </c>
+      <c r="BF181" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>GRNDLVP-0077</t>
+          <t>LVP-GRAN-0014</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -21799,7 +23556,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>GRNDENTREPRERAINMOOR</t>
+          <t>GRND7ENTREPRENEURRAINMOOR</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -21894,13 +23651,23 @@
       <c r="BC182" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Glassfibre core, Made in Korea. Material type set to 'Dry-back vinyl' per the Woden-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE182" t="inlineStr">
+        <is>
+          <t>recM1psdOt5QO93hK</t>
+        </is>
+      </c>
+      <c r="BF182" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>GRNDLVP-0078</t>
+          <t>LVP-GRAN-0015</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -21920,7 +23687,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>GRNDENTREPRESTONEVEIL</t>
+          <t>GRND7ENTREPRENEURSTONEVEIL</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -22015,13 +23782,23 @@
       <c r="BC183" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Glassfibre core, Made in Korea. Material type set to 'Dry-back vinyl' per the Woden-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE183" t="inlineStr">
+        <is>
+          <t>recwgLW2k3BTVFPwP</t>
+        </is>
+      </c>
+      <c r="BF183" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>GRNDLVP-0079</t>
+          <t>LVP-GRAN-0016</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -22041,7 +23818,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>GRNDENTREPREWOODMERE</t>
+          <t>GRND7ENTREPRENEURWOODMERE</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -22136,13 +23913,23 @@
       <c r="BC184" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Glassfibre core, Made in Korea. Material type set to 'Dry-back vinyl' per the Woden-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE184" t="inlineStr">
+        <is>
+          <t>recO6q2AEFDQvNwNB</t>
+        </is>
+      </c>
+      <c r="BF184" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>GRNDLVP-0080</t>
+          <t>LVP-GRAN-0017</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -22162,7 +23949,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>GRNDTIMELESSACACIA</t>
+          <t>GRND7TIMELESSACACIA</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -22249,13 +24036,23 @@
       <c r="BC185" t="inlineStr">
         <is>
           <t>Made in Korea. Material type set to 'Loose-lay vinyl' per the Woden/Purelux-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE185" t="inlineStr">
+        <is>
+          <t>recwNVofiRfE3zjFf</t>
+        </is>
+      </c>
+      <c r="BF185" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>GRNDLVP-0081</t>
+          <t>LVP-GRAN-0018</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -22275,7 +24072,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>GRNDTIMELESSAPPALACHIANMOUNTAINS</t>
+          <t>GRND7TIMELESSAPPALACHIANMOUNTAINS</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -22362,13 +24159,23 @@
       <c r="BC186" t="inlineStr">
         <is>
           <t>Made in Korea. Material type set to 'Loose-lay vinyl' per the Woden/Purelux-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE186" t="inlineStr">
+        <is>
+          <t>recByr2x0TAfQ7jkF</t>
+        </is>
+      </c>
+      <c r="BF186" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>GRNDLVP-0082</t>
+          <t>LVP-GRAN-0019</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -22388,7 +24195,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>GRNDTIMELESSBARNBOARD</t>
+          <t>GRND7TIMELESSBARNBOARD</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -22475,13 +24282,23 @@
       <c r="BC187" t="inlineStr">
         <is>
           <t>Made in Korea. Material type set to 'Loose-lay vinyl' per the Woden/Purelux-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE187" t="inlineStr">
+        <is>
+          <t>rec0K3vUMnwyV1U9A</t>
+        </is>
+      </c>
+      <c r="BF187" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>GRNDLVP-0083</t>
+          <t>LVP-GRAN-0020</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -22501,7 +24318,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>GRNDTIMELESSCLOUDYSKY</t>
+          <t>GRND7TIMELESSCLOUDYSKY</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -22588,13 +24405,23 @@
       <c r="BC188" t="inlineStr">
         <is>
           <t>Made in Korea. Material type set to 'Loose-lay vinyl' per the Woden/Purelux-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE188" t="inlineStr">
+        <is>
+          <t>recUH0cbXi9i2brIw</t>
+        </is>
+      </c>
+      <c r="BF188" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>GRNDLVP-0084</t>
+          <t>LVP-GRAN-0021</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -22614,7 +24441,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>GRNDTIMELESSEXOTICWALNUT</t>
+          <t>GRND7TIMELESSEXOTICWALNUT</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -22701,13 +24528,23 @@
       <c r="BC189" t="inlineStr">
         <is>
           <t>Made in Korea. Material type set to 'Loose-lay vinyl' per the Woden/Purelux-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE189" t="inlineStr">
+        <is>
+          <t>recDXT0aXGjOuQMBd</t>
+        </is>
+      </c>
+      <c r="BF189" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>GRNDLVP-0085</t>
+          <t>LVP-GRAN-0022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -22727,7 +24564,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>GRNDTIMELESSHAZE</t>
+          <t>GRND7TIMELESSHAZE</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -22814,13 +24651,23 @@
       <c r="BC190" t="inlineStr">
         <is>
           <t>Made in Korea. Material type set to 'Loose-lay vinyl' per the Woden/Purelux-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE190" t="inlineStr">
+        <is>
+          <t>recnAfEHG1PG3rwJE</t>
+        </is>
+      </c>
+      <c r="BF190" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>GRNDLVP-0086</t>
+          <t>LVP-GRAN-0023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -22840,7 +24687,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>GRNDTIMELESSHAZELNUT</t>
+          <t>GRND7TIMELESSHAZELNUT</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -22927,13 +24774,23 @@
       <c r="BC191" t="inlineStr">
         <is>
           <t>Made in Korea. Material type set to 'Loose-lay vinyl' per the Woden/Purelux-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE191" t="inlineStr">
+        <is>
+          <t>reccNCN7Jkcyub7vT</t>
+        </is>
+      </c>
+      <c r="BF191" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>GRNDLVP-0087</t>
+          <t>LVP-GRAN-0024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -22953,7 +24810,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>GRNDTIMELESSNORTHERNOAK</t>
+          <t>GRND7TIMELESSNORTHERNOAK</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -23040,13 +24897,23 @@
       <c r="BC192" t="inlineStr">
         <is>
           <t>Made in Korea. Material type set to 'Loose-lay vinyl' per the Woden/Purelux-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE192" t="inlineStr">
+        <is>
+          <t>recIwHaohMShCTlAx</t>
+        </is>
+      </c>
+      <c r="BF192" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>GRNDLVP-0088</t>
+          <t>LVP-GRAN-0025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -23066,7 +24933,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>GRNDTIMELESSSMOKEDOAK</t>
+          <t>GRND7TIMELESSSMOKEDOAK</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -23153,13 +25020,23 @@
       <c r="BC193" t="inlineStr">
         <is>
           <t>Made in Korea. Material type set to 'Loose-lay vinyl' per the Woden/Purelux-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE193" t="inlineStr">
+        <is>
+          <t>recACBkC1gG2L26g2</t>
+        </is>
+      </c>
+      <c r="BF193" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>GRNDLVP-0089</t>
+          <t>LVP-GRAN-0026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -23179,7 +25056,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>GRNDTIMELESSWEATHEREDOAK</t>
+          <t>GRND7TIMELESSWEATHEREDOAK</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -23266,13 +25143,23 @@
       <c r="BC194" t="inlineStr">
         <is>
           <t>Made in Korea. Material type set to 'Loose-lay vinyl' per the Woden/Purelux-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE194" t="inlineStr">
+        <is>
+          <t>recXrpBwn3TmGsZ7m</t>
+        </is>
+      </c>
+      <c r="BF194" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>GRNDLVP-0090</t>
+          <t>LVP-GRAN-0027</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -23292,7 +25179,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>GRNDULTIMATEFRIDAYHARBOR</t>
+          <t>GRND7ULTIMATEFRIDAYHARBOR</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -23384,13 +25271,23 @@
       <c r="BC195" t="inlineStr">
         <is>
           <t>Made in Korea. Material type set to 'Loose-lay vinyl' per the Woden/Purelux-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE195" t="inlineStr">
+        <is>
+          <t>recEt2kt00mmcnQE4</t>
+        </is>
+      </c>
+      <c r="BF195" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>GRNDLVP-0091</t>
+          <t>LVP-GRAN-0028</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -23410,7 +25307,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>GRNDULTIMATEHUMBERBAY</t>
+          <t>GRND7ULTIMATEHUMBERBAY</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -23502,13 +25399,23 @@
       <c r="BC196" t="inlineStr">
         <is>
           <t>Made in Korea. Material type set to 'Loose-lay vinyl' per the Woden/Purelux-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE196" t="inlineStr">
+        <is>
+          <t>rec0GNSBpT7rcWuob</t>
+        </is>
+      </c>
+      <c r="BF196" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>GRNDLVP-0092</t>
+          <t>LVP-GRAN-0029</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -23528,7 +25435,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>GRNDULTIMATEHIGHPARK</t>
+          <t>GRND7ULTIMATEHIGHPARK</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -23620,13 +25527,23 @@
       <c r="BC197" t="inlineStr">
         <is>
           <t>Made in Korea. Material type set to 'Loose-lay vinyl' per the Woden/Purelux-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE197" t="inlineStr">
+        <is>
+          <t>rectGtZphApMR0vMs</t>
+        </is>
+      </c>
+      <c r="BF197" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>GRNDLVP-0093</t>
+          <t>LVP-GRAN-0030</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -23646,7 +25563,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>GRNDULTIMATELAKESHOREBLVD</t>
+          <t>GRND7ULTIMATELAKESHOREBLVD</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -23738,13 +25655,23 @@
       <c r="BC198" t="inlineStr">
         <is>
           <t>Made in Korea. Material type set to 'Loose-lay vinyl' per the Woden/Purelux-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE198" t="inlineStr">
+        <is>
+          <t>recPSHw8KpwJf1sqf</t>
+        </is>
+      </c>
+      <c r="BF198" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>GRNDLVP-0094</t>
+          <t>LVP-GRAN-0031</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -23764,7 +25691,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>GRNDULTIMATELAKEVIEW</t>
+          <t>GRND7ULTIMATELAKEVIEW</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -23856,13 +25783,23 @@
       <c r="BC199" t="inlineStr">
         <is>
           <t>Made in Korea. Material type set to 'Loose-lay vinyl' per the Woden/Purelux-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE199" t="inlineStr">
+        <is>
+          <t>recus505aLyhFyHUe</t>
+        </is>
+      </c>
+      <c r="BF199" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>GRNDLVP-0095</t>
+          <t>LVP-GRAN-0032</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -23882,7 +25819,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>GRNDULTIMATEPIER17</t>
+          <t>GRND7ULTIMATEPIER17</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -23974,13 +25911,23 @@
       <c r="BC200" t="inlineStr">
         <is>
           <t>Made in Korea. Material type set to 'Loose-lay vinyl' per the Woden/Purelux-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE200" t="inlineStr">
+        <is>
+          <t>recwzM02dBHKaYY0Z</t>
+        </is>
+      </c>
+      <c r="BF200" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>GRNDLVP-0096</t>
+          <t>LVP-GRAN-0033</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -24000,7 +25947,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>GRNDULTIMATESUNNYSIDE</t>
+          <t>GRND7ULTIMATESUNNYSIDE</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -24092,13 +26039,23 @@
       <c r="BC201" t="inlineStr">
         <is>
           <t>Made in Korea. Material type set to 'Loose-lay vinyl' per the Woden/Purelux-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE201" t="inlineStr">
+        <is>
+          <t>rec5OKPLXUaRyw10f</t>
+        </is>
+      </c>
+      <c r="BF201" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>GRNDLVP-0097</t>
+          <t>LVP-GRAN-0034</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -24118,7 +26075,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>GRNDULTIMATESUMMERWHARF</t>
+          <t>GRND7ULTIMATESUMMERWHARF</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -24210,13 +26167,23 @@
       <c r="BC202" t="inlineStr">
         <is>
           <t>Made in Korea. Material type set to 'Loose-lay vinyl' per the Woden/Purelux-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE202" t="inlineStr">
+        <is>
+          <t>recePcHRuCJUzG0WQ</t>
+        </is>
+      </c>
+      <c r="BF202" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>GRNDLVT-0004</t>
+          <t>LVP-GRAN-0035</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -24236,7 +26203,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>GRNDULTIMATEARCHBRIDGE</t>
+          <t>GRND12ULTIMATEARCHBRIDGE</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -24328,13 +26295,23 @@
       <c r="BC203" t="inlineStr">
         <is>
           <t>12"x24" tile-format loose-lay vinyl -&gt; Category=LVT. Made in Korea. Material type set to 'Loose-lay vinyl' per the Woden/Purelux-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE203" t="inlineStr">
+        <is>
+          <t>recMzzVRk9KkuHWdx</t>
+        </is>
+      </c>
+      <c r="BF203" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>GRNDLVT-0005</t>
+          <t>LVP-GRAN-0036</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -24354,7 +26331,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>GRNDULTIMATESKYLINE</t>
+          <t>GRND12ULTIMATESKYLINE</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -24446,13 +26423,23 @@
       <c r="BC204" t="inlineStr">
         <is>
           <t>12"x24" tile-format loose-lay vinyl -&gt; Category=LVT. Made in Korea. Material type set to 'Loose-lay vinyl' per the Woden/Purelux-precedent value; confirm acceptable in live schema.</t>
+        </is>
+      </c>
+      <c r="BE204" t="inlineStr">
+        <is>
+          <t>rec2hTiV4pyd2YLF5</t>
+        </is>
+      </c>
+      <c r="BF204" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>GRNDLAM-0001</t>
+          <t>LAM-GRAN-0001</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -24472,7 +26459,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>GRND12COLLECARLESNATURAL</t>
+          <t>GRND12MM12COLLECTIONARLESNATURAL</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -24548,13 +26535,23 @@
       <c r="AV205" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE205" t="inlineStr">
+        <is>
+          <t>recixZwavXI4kvp8H</t>
+        </is>
+      </c>
+      <c r="BF205" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>GRNDLAM-0002</t>
+          <t>LAM-GRAN-0003</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -24574,7 +26571,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>GRND12COLLECFADOGAVIA</t>
+          <t>GRND12MM12COLLECTIONFADOGAVIA</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -24650,13 +26647,23 @@
       <c r="AV206" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE206" t="inlineStr">
+        <is>
+          <t>recos0lzPMNAzKJUH</t>
+        </is>
+      </c>
+      <c r="BF206" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>GRNDLAM-0003</t>
+          <t>LAM-GRAN-0004</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -24676,7 +26683,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>GRND12COLLECFADOSOTAVENTO</t>
+          <t>GRND12MM12COLLECTIONFADOSOTAVENTO</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -24752,13 +26759,23 @@
       <c r="AV207" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE207" t="inlineStr">
+        <is>
+          <t>recNe4Ke0sRJjEIUN</t>
+        </is>
+      </c>
+      <c r="BF207" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>GRNDLAM-0004</t>
+          <t>LAM-GRAN-0005</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -24778,7 +26795,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>GRND12COLLECKALASALBAR</t>
+          <t>GRND12MM12COLLECTIONKALASALBAR</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -24854,13 +26871,23 @@
       <c r="AV208" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE208" t="inlineStr">
+        <is>
+          <t>recEmHVn1vNGpvCDt</t>
+        </is>
+      </c>
+      <c r="BF208" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>GRNDLAM-0005</t>
+          <t>LAM-GRAN-0006</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -24880,7 +26907,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>GRND12COLLECKALMARGRIS</t>
+          <t>GRND12MM12COLLECTIONKALMARGRIS</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -24956,13 +26983,23 @@
       <c r="AV209" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE209" t="inlineStr">
+        <is>
+          <t>recDEJ8hKH3DnbB7d</t>
+        </is>
+      </c>
+      <c r="BF209" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>GRNDLAM-0006</t>
+          <t>LAM-GRAN-0007</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -24982,7 +27019,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>GRND12COLLECKALASNOZ</t>
+          <t>GRND12MM12COLLECTIONKALASNOZ</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -25058,13 +27095,23 @@
       <c r="AV210" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE210" t="inlineStr">
+        <is>
+          <t>recphjAQEHoPoZCOn</t>
+        </is>
+      </c>
+      <c r="BF210" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>GRNDLAM-0007</t>
+          <t>LAM-GRAN-0008</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -25084,7 +27131,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>GRND12COLLECROBLETWILIGHT</t>
+          <t>GRND12MM12COLLECTIONROBLETWILIGHT</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -25160,13 +27207,23 @@
       <c r="AV211" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE211" t="inlineStr">
+        <is>
+          <t>recOTYmFCscDPrdhL</t>
+        </is>
+      </c>
+      <c r="BF211" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>GRNDLAM-0008</t>
+          <t>LAM-GRAN-0009</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -25186,7 +27243,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>GRND12COLLECVIENADORADO</t>
+          <t>GRND12MM12COLLECTIONVIENADORADO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -25262,13 +27319,23 @@
       <c r="AV212" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE212" t="inlineStr">
+        <is>
+          <t>recGwoBfFjXuxCQfL</t>
+        </is>
+      </c>
+      <c r="BF212" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>GRNDLAM-0009</t>
+          <t>LAM-GRAN-0010</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -25288,7 +27355,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>GRND12COLLECWEXFORDTOSTADO</t>
+          <t>GRND12MM12COLLECTIONWEXFORDTOSTADO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -25364,13 +27431,23 @@
       <c r="AV213" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE213" t="inlineStr">
+        <is>
+          <t>recvIP7CSzUgMcTYC</t>
+        </is>
+      </c>
+      <c r="BF213" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>GRNDLAM-0010</t>
+          <t>LAM-GRAN-0011</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -25390,7 +27467,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>GRNDXXLCOLLEANETO</t>
+          <t>GRND12MMXXLANETO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -25466,13 +27543,23 @@
       <c r="AV214" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE214" t="inlineStr">
+        <is>
+          <t>recHIY8f8NM83xQ6H</t>
+        </is>
+      </c>
+      <c r="BF214" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>GRNDLAM-0011</t>
+          <t>LAM-GRAN-0012</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -25492,7 +27579,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>GRNDXXLCOLLECERVINO</t>
+          <t>GRND12MMXXLCERVINO</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -25568,13 +27655,23 @@
       <c r="AV215" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE215" t="inlineStr">
+        <is>
+          <t>recNeuvucASNCxU25</t>
+        </is>
+      </c>
+      <c r="BF215" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>GRNDLAM-0012</t>
+          <t>LAM-GRAN-0013</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -25594,7 +27691,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>GRNDXXLCOLLEDENALI</t>
+          <t>GRND12MMXXLDENALI</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -25670,13 +27767,23 @@
       <c r="AV216" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE216" t="inlineStr">
+        <is>
+          <t>reced2KFqtKVsxzdV</t>
+        </is>
+      </c>
+      <c r="BF216" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>GRNDLAM-0013</t>
+          <t>LAM-GRAN-0014</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -25696,7 +27803,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>GRNDXXLCOLLEELGON</t>
+          <t>GRND12MMXXLELGON</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -25772,13 +27879,23 @@
       <c r="AV217" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE217" t="inlineStr">
+        <is>
+          <t>recjbM4UyEhKMwOLH</t>
+        </is>
+      </c>
+      <c r="BF217" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>GRNDLAM-0014</t>
+          <t>LAM-GRAN-0015</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -25798,7 +27915,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>GRNDXXLCOLLEEVEREST</t>
+          <t>GRND12MMXXLEVEREST</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -25874,13 +27991,23 @@
       <c r="AV218" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE218" t="inlineStr">
+        <is>
+          <t>recXNSfawycS25hoF</t>
+        </is>
+      </c>
+      <c r="BF218" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>GRNDLAM-0015</t>
+          <t>LAM-GRAN-0016</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -25900,7 +28027,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>GRNDXXLCOLLEFUJI</t>
+          <t>GRND12MMXXLFUJI</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -25976,13 +28103,23 @@
       <c r="AV219" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE219" t="inlineStr">
+        <is>
+          <t>recxTVxeHsbLfXnDI</t>
+        </is>
+      </c>
+      <c r="BF219" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>GRNDLAM-0016</t>
+          <t>LAM-GRAN-0017</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -26002,7 +28139,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>GRNDXXLCOLLEKILIMANJARO</t>
+          <t>GRND12MMXXLKILIMANJARO</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -26078,13 +28215,23 @@
       <c r="AV220" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE220" t="inlineStr">
+        <is>
+          <t>reclV39UW8z6Fr7b5</t>
+        </is>
+      </c>
+      <c r="BF220" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>GRNDLAM-0017</t>
+          <t>LAM-GRAN-0018</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -26104,7 +28251,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>GRNDXXLCOLLEKINGPEAK</t>
+          <t>GRND12MMXXLKINGPEAK</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -26180,13 +28327,23 @@
       <c r="AV221" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE221" t="inlineStr">
+        <is>
+          <t>recrwjXZn0gEtnkQc</t>
+        </is>
+      </c>
+      <c r="BF221" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>GRNDLAM-0018</t>
+          <t>LAM-GRAN-0019</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -26206,7 +28363,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>GRNDXXLCOLLELOGAN</t>
+          <t>GRND12MMXXLLOGAN</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -26282,13 +28439,23 @@
       <c r="AV222" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE222" t="inlineStr">
+        <is>
+          <t>recrD3o0gbn4a0efH</t>
+        </is>
+      </c>
+      <c r="BF222" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>GRNDLAM-0019</t>
+          <t>LAM-GRAN-0020</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -26308,7 +28475,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>GRNDXXLCOLLEMONTBLANC</t>
+          <t>GRND12MMXXLMONTBLANC</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -26384,13 +28551,23 @@
       <c r="AV223" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BE223" t="inlineStr">
+        <is>
+          <t>recUf1v4hYV2NSv2u</t>
+        </is>
+      </c>
+      <c r="BF223" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>GRNDLAM-0020</t>
+          <t>LAM-GRAN-0021</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -26410,7 +28587,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>GRNDAQUAMATEADELAIDE</t>
+          <t>GRND12MMAQUAMATEADELAIDE</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -26499,13 +28676,23 @@
       <c r="BC224" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. 72hr Water Resistant EIR HDF laminate -- Material type set to 'Water-Resistant Core'; Waterproof left FALSE per global rule (water-resistant is not the same as waterproof).</t>
+        </is>
+      </c>
+      <c r="BE224" t="inlineStr">
+        <is>
+          <t>recVe2VycDGeaEu6D</t>
+        </is>
+      </c>
+      <c r="BF224" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>GRNDLAM-0021</t>
+          <t>LAM-GRAN-0022</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -26525,7 +28712,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>GRNDAQUAMATEALICESPRINGS</t>
+          <t>GRND12MMAQUAMATEALICESPRINGS</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -26614,13 +28801,23 @@
       <c r="BC225" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. 72hr Water Resistant EIR HDF laminate -- Material type set to 'Water-Resistant Core'; Waterproof left FALSE per global rule (water-resistant is not the same as waterproof).</t>
+        </is>
+      </c>
+      <c r="BE225" t="inlineStr">
+        <is>
+          <t>rec3dgvUu8ud9fZK3</t>
+        </is>
+      </c>
+      <c r="BF225" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>GRNDLAM-0022</t>
+          <t>LAM-GRAN-0023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -26640,7 +28837,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>GRNDAQUAMATEBRISBANE</t>
+          <t>GRND12MMAQUAMATEBRISBANE</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -26729,13 +28926,23 @@
       <c r="BC226" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. 72hr Water Resistant EIR HDF laminate -- Material type set to 'Water-Resistant Core'; Waterproof left FALSE per global rule (water-resistant is not the same as waterproof).</t>
+        </is>
+      </c>
+      <c r="BE226" t="inlineStr">
+        <is>
+          <t>recWdHn7oGPphqPMX</t>
+        </is>
+      </c>
+      <c r="BF226" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>GRNDLAM-0023</t>
+          <t>LAM-GRAN-0024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -26755,7 +28962,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>GRNDAQUAMATECAIRNS</t>
+          <t>GRND12MMAQUAMATECAIRNS</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -26844,13 +29051,23 @@
       <c r="BC227" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. 72hr Water Resistant EIR HDF laminate -- Material type set to 'Water-Resistant Core'; Waterproof left FALSE per global rule (water-resistant is not the same as waterproof).</t>
+        </is>
+      </c>
+      <c r="BE227" t="inlineStr">
+        <is>
+          <t>recjXy03aTyBpgPrf</t>
+        </is>
+      </c>
+      <c r="BF227" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>GRNDLAM-0024</t>
+          <t>LAM-GRAN-0025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -26870,7 +29087,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>GRNDAQUAMATECANBERRA</t>
+          <t>GRND12MMAQUAMATECANBERRA</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -26959,13 +29176,23 @@
       <c r="BC228" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. 72hr Water Resistant EIR HDF laminate -- Material type set to 'Water-Resistant Core'; Waterproof left FALSE per global rule (water-resistant is not the same as waterproof).</t>
+        </is>
+      </c>
+      <c r="BE228" t="inlineStr">
+        <is>
+          <t>recN08dH2KlFUfu6B</t>
+        </is>
+      </c>
+      <c r="BF228" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>GRNDLAM-0025</t>
+          <t>LAM-GRAN-0026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -26985,7 +29212,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>GRNDAQUAMATEDARWIN</t>
+          <t>GRND12MMAQUAMATEDARWIN</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -27074,13 +29301,23 @@
       <c r="BC229" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. 72hr Water Resistant EIR HDF laminate -- Material type set to 'Water-Resistant Core'; Waterproof left FALSE per global rule (water-resistant is not the same as waterproof).</t>
+        </is>
+      </c>
+      <c r="BE229" t="inlineStr">
+        <is>
+          <t>recsXn0EAT6EptTef</t>
+        </is>
+      </c>
+      <c r="BF229" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>GRNDLAM-0026</t>
+          <t>LAM-GRAN-0027</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -27100,7 +29337,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>GRNDAQUAMATEHOBART</t>
+          <t>GRND12MMAQUAMATEHOBART</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -27189,13 +29426,23 @@
       <c r="BC230" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. 72hr Water Resistant EIR HDF laminate -- Material type set to 'Water-Resistant Core'; Waterproof left FALSE per global rule (water-resistant is not the same as waterproof).</t>
+        </is>
+      </c>
+      <c r="BE230" t="inlineStr">
+        <is>
+          <t>reczwlvhIikBRkGSY</t>
+        </is>
+      </c>
+      <c r="BF230" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>GRNDLAM-0027</t>
+          <t>LAM-GRAN-0028</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -27215,7 +29462,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>GRNDAQUAMATEMELBOURNE</t>
+          <t>GRND12MMAQUAMATEMELBOURNE</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -27304,13 +29551,23 @@
       <c r="BC231" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. 72hr Water Resistant EIR HDF laminate -- Material type set to 'Water-Resistant Core'; Waterproof left FALSE per global rule (water-resistant is not the same as waterproof).</t>
+        </is>
+      </c>
+      <c r="BE231" t="inlineStr">
+        <is>
+          <t>rec5XmPqgRJR4892s</t>
+        </is>
+      </c>
+      <c r="BF231" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>GRNDLAM-0028</t>
+          <t>LAM-GRAN-0029</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -27330,7 +29587,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>GRNDAQUAMATEPERTH</t>
+          <t>GRND12MMAQUAMATEPERTH</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -27419,6 +29676,16 @@
       <c r="BC232" t="inlineStr">
         <is>
           <t>SALE item. No regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. 72hr Water Resistant EIR HDF laminate -- Material type set to 'Water-Resistant Core'; Waterproof left FALSE per global rule (water-resistant is not the same as waterproof).</t>
+        </is>
+      </c>
+      <c r="BE232" t="inlineStr">
+        <is>
+          <t>recLg1CS4SRjYIUNg</t>
+        </is>
+      </c>
+      <c r="BF232" t="inlineStr">
+        <is>
+          <t>matched</t>
         </is>
       </c>
     </row>

--- a/ingest/2026-09-03/grandeur_airtable_upload_2026-09-03.xlsx
+++ b/ingest/2026-09-03/grandeur_airtable_upload_2026-09-03.xlsx
@@ -789,6 +789,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>56647347-cc50-4eac-b402-4b7c4ac8a568</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>GRND65EWOBARBADOS</t>
@@ -907,6 +912,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b63420110</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>GRND65EWOBORABORA</t>
@@ -1025,6 +1035,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6c33a689</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>GRND65EWOSANTORINI</t>
@@ -1143,6 +1158,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6c4f4912</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>GRND65EWOSARDINIA</t>
@@ -1261,6 +1281,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6c7dd82d</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>GRND65EWOSTLUCIA</t>
@@ -1379,6 +1404,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6ce6634b</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>GRND65EWOTAHITI</t>
@@ -1497,6 +1527,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6d4e7c57</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>GRND65EWOWHITEISLAND</t>
@@ -1615,6 +1650,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>c8645e67-b982-4d9f-a8a8-f90ea5da608a</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>GRND6EWOLAGUNABEACH</t>
@@ -1733,6 +1773,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>06b7f4bc-c974-45cb-a8a5-82514af41d1e</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>GRND6EWOSANTACRUZ</t>
@@ -1851,6 +1896,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b61b6b476</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>GRND65NAHNATURAL</t>
@@ -1982,6 +2032,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b617662c4</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>GRND65NAHHARVEST</t>
@@ -2113,6 +2168,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b61a226dc</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>GRND65NAHMANE</t>
@@ -2244,6 +2304,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>40a9301e-9c7a-41fc-be3d-d11d66ae7569</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>GRND65NAHNORTHWEST</t>
@@ -2375,6 +2440,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b61cf6d25</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>GRND65NAHOWL</t>
@@ -2506,6 +2576,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b62d22f3f</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>GRND6HMRUM</t>
@@ -2642,6 +2717,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>db9b4e9d-1752-42e7-a611-da00a9e2a415</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>GRND75AOHONEYCOMB</t>
@@ -2760,6 +2840,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>200259e8-37e1-4713-885d-bd9cd8a43d46</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>GRND75AOSANDYSILK</t>
@@ -2878,6 +2963,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>c2b3e992-e3dd-426f-84b1-e32cb7f589c5</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>GRND75AOCASCADE</t>
@@ -3009,6 +3099,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>67b2f64b-4ae5-490f-a64a-bd8129b7581d</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>GRND6EWOCOCOABEACH</t>
@@ -3127,6 +3222,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1c035705-7d40-4c57-8dba-2f9f55ca585b</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>GRND6EWOCLEARWATER</t>
@@ -3245,6 +3345,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>98e682df-4574-41ea-87c7-c9a3ca49f42a</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>GRND6EWODESTIN</t>
@@ -3363,6 +3468,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>6eb7ac42-78e3-4868-b687-ea155c8b0b86</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>GRND6EWOKEYWEST</t>
@@ -3481,6 +3591,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>8463d341-bdd0-4248-8130-746c36055773</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>GRND6EWOMIAMI</t>
@@ -3599,6 +3714,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>65377fd3-16f6-4b03-a262-0d7ede025402</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>GRND6EWOPANAMACITY</t>
@@ -3717,6 +3837,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>15a6a2ec-8d78-48a7-8423-58dcc1b23f62</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>GRND75EWOMORAINE</t>
@@ -3853,6 +3978,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>6d6b4916-ec07-48a1-89d8-d2e107070a57</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>GRND75EWOBLUEMOUNTAIN</t>
@@ -3984,6 +4114,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6109aac9</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>GRND75NAHALPINE</t>
@@ -4102,6 +4237,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6133d236</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>GRND75NAHCROWN</t>
@@ -4220,6 +4360,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b618c2b12</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>GRND75NAHICEFALL</t>
@@ -4338,6 +4483,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b61e688ac</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>GRND75NAHSUMMIT</t>
@@ -4456,6 +4606,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>10a44829-7326-45a8-8704-b35c3011ba01</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>GRND75NAHNIMBUS</t>
@@ -4587,6 +4742,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b61fca894</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>GRND75HMARIES</t>
@@ -4710,6 +4870,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6211d1c9</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>GRND75HMLEO</t>
@@ -4833,6 +4998,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6226c360</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>GRND75HMLIBRA</t>
@@ -4956,6 +5126,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6257f2a5</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>GRND75HMTAURUS</t>
@@ -5079,6 +5254,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6243683e</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>GRND75HMSCORPIO</t>
@@ -5202,6 +5382,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b626fc2c5</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>GRND75HMTHUNDERCLOUD</t>
@@ -5333,6 +5518,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b63b07cb4</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>GRND75EWOCLIFF</t>
@@ -5451,6 +5641,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6bceaf92</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>GRND75EWOPETRICHOR</t>
@@ -5569,6 +5764,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6cb0f2a1</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>GRND75EWOSTRATUS</t>
@@ -5687,6 +5887,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6aeba2b8</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>GRND75EWOLAGOM</t>
@@ -5805,6 +6010,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6bb5fa1a</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>GRND75EWONORDICSAND</t>
@@ -5923,6 +6133,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>7f10b490-b11d-4b8a-8e59-f5287afebce8</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>GRND75EWOPANDO</t>
@@ -6041,6 +6256,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>367bd8a8-1208-4179-8636-da9581066c56</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>GRND75EWOTUNDRA</t>
@@ -6159,6 +6379,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6ab8bc59</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>GRND75EWOKINGSLANDING</t>
@@ -6277,6 +6502,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6ccbd9e8</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>GRND75EWOSUNSPEAR</t>
@@ -6395,6 +6625,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6aeba2b8</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>GRND5EWOLAGOMHB</t>
@@ -6518,6 +6753,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6bb5fa1a</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>GRND5EWONORDICSANDHB</t>
@@ -6641,6 +6881,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>7f10b490-b11d-4b8a-8e59-f5287afebce8</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>GRND5EWOPANDOHB</t>
@@ -6764,6 +7009,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>367bd8a8-1208-4179-8636-da9581066c56</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>GRND5EWOTUNDRAHB</t>
@@ -6887,6 +7137,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1927955a-c997-4c30-a113-51cfa6d1cd63</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>GRND6EWONAPAVALLEYCHEVRON</t>
@@ -7010,6 +7265,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>490a8512-5096-4a04-bfe4-d9b1dbdf13a3</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>GRND95EWOBANFF</t>
@@ -7133,6 +7393,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>0b926671-55cd-4cfd-bd1c-389daf725375</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>GRND95EWOCAPEBRETON</t>
@@ -7256,6 +7521,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>5dd57066-d105-4667-acda-b0300bb772b1</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>GRND95EWOMONTTREMBLANT</t>
@@ -7379,6 +7649,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>8f5c9008-3c44-41c1-923b-271d0c5151da</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>GRND95EWOPACIFICRIM</t>
@@ -7502,6 +7777,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>988f35d4-190b-48f8-adcc-350e71de3940</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>GRND95EWOWHISTLER</t>
@@ -7625,6 +7905,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>a1d9916b-ed0e-4ec3-9373-de7b96db73cf</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
           <t>GRND95EWOYOHO</t>
@@ -7748,6 +8033,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>92442d0a-a66c-46b8-bcb1-dfe91b0a2faf</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
           <t>GRND75EWOSANDBAR</t>
@@ -7866,6 +8156,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>e7c32a4a-16f6-4b26-8370-eb3cae759bf1</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
           <t>GRND75EWOSILVA</t>
@@ -7984,6 +8279,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>6f1a2c8f-508a-40bd-a581-15abbd829603</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
           <t>GRND75EWOANACAPRI</t>
@@ -8115,6 +8415,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>468e7a95-81c3-4604-a380-a945f3bb43f9</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>GRND75EWOMILAN</t>
@@ -8246,6 +8551,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>af8d627b-4fa0-47da-8922-d915093ff448</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>GRND75EWOAZURECOAST</t>
@@ -8377,6 +8687,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>e13ac32d-2843-4154-b111-1865909596f9</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>GRND75EWOMOROCCOSAND</t>
@@ -8508,6 +8823,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>f6c32fba-09c6-47b7-a14e-bca71e03fd2e</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>GRND6EWOMOROCCOSAND</t>
@@ -8639,6 +8959,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>4ddb1936-73fb-4f83-8032-ab92085605be</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>GRND6EWOBAROSSA</t>
@@ -8757,6 +9082,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>db38c309-f3b2-41fb-81b3-ea53b734bcdd</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>GRND6EWOBURGUNDY</t>
@@ -8875,6 +9205,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>48280127-6dfe-49dd-8ab8-78ee9b372d5a</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>GRND6EWONAPAVALLEY</t>
@@ -8993,6 +9328,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>a0714599-ef55-45fe-921d-2e8b2477513b</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
           <t>GRND6EWOSONOMA</t>
@@ -9229,6 +9569,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>4ddb1936-73fb-4f83-8032-ab92085605be</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>GRND75EWOBAROSSA</t>
@@ -9347,6 +9692,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>db38c309-f3b2-41fb-81b3-ea53b734bcdd</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
           <t>GRND75EWOBURGUNDY</t>
@@ -9465,6 +9815,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>19caaaf1-b12e-4c09-9dd7-695dc2301548</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
           <t>GRND75EWONAPAVALLEY</t>
@@ -9583,6 +9938,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>9273de7e-d9ca-4f81-8f48-cc00e7455c54</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
           <t>GRND75EWOSONOMA</t>
@@ -9819,6 +10179,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>4ddb1936-73fb-4f83-8032-ab92085605be</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>GRND6EWOBAROSSAHB</t>
@@ -9942,6 +10307,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>db38c309-f3b2-41fb-81b3-ea53b734bcdd</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>GRND6EWOBURGUNDYHB</t>
@@ -10065,6 +10435,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1927955a-c997-4c30-a113-51cfa6d1cd63</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
           <t>GRND6EWONAPAVALLEYHB</t>
@@ -10188,6 +10563,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>fe500b63-e2bd-4c71-b9ad-a542c0aa5897</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
           <t>GRND6EWOSONOMAHB</t>
@@ -10311,6 +10691,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>5ae28880-418b-46ce-9cb1-b33434d2e69c</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
           <t>GRND75AOROSEDALE</t>
@@ -10429,6 +10814,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>e0bd75ab-1037-4001-8923-7a8f769854c5</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>GRND5WOASPEN</t>
@@ -10552,6 +10942,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>b9f666a2-d314-4fd4-bd7d-260208cdad98</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>GRND5WOELM</t>
@@ -10675,6 +11070,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>f55ad67d-6b03-4473-a7fc-c0c5e06a7ed8</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>GRND5WOHEMLOCK</t>
@@ -10798,6 +11198,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>864fcdbd-658b-40b5-b9ae-ae6019ed19be</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
           <t>GRND5WOSYCAMORE</t>
@@ -10921,6 +11326,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>d6f96d1b-f923-4dcf-b69c-3518f64b726a</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
           <t>GRND75WOBRONZEDUST</t>
@@ -11039,6 +11449,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>4ac3d94a-0fc0-40a9-a347-95181631957b</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
           <t>GRND75WOCARRARA</t>
@@ -11157,6 +11572,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2267d47f-7487-4ea9-bc58-caf0621f9715</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
           <t>GRND75WOCLAYBORN</t>
@@ -11275,6 +11695,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>8133ed4c-d624-434d-b87d-d6bc27f7a7ba</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
           <t>GRND75WOTERRACOTTA</t>
@@ -12337,6 +12762,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6e0344e6</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
           <t>GRND425NAROAMARETTO</t>
@@ -12447,6 +12877,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6e1c8bac</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>GRND425NAROGUNSTOCK</t>
@@ -12557,6 +12992,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>946f5afb-4bb6-495b-bf01-2d8a36ad672a</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr">
         <is>
           <t>GRND425NAROLATTE</t>
@@ -12667,6 +13107,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6e725224</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr">
         <is>
           <t>GRND425NAROMOKA</t>
@@ -12777,6 +13222,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b6e8abb9b</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
           <t>GRND425NAROTREEBARK</t>
@@ -12887,6 +13337,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1cdf4689-1d69-42da-a680-20e49f9d6bfb</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
           <t>GRND425NAROWALNUT</t>
@@ -13002,6 +13457,11 @@
           <t>CDW340-2</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>c02e1829-666a-4129-8bfe-77985e67786b</t>
+        </is>
+      </c>
       <c r="G103" t="inlineStr">
         <is>
           <t>GRND7ATLANTICCDW3402</t>
@@ -13276,6 +13736,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>8dfbeb18-83a7-427f-8c23-dbb4ef538ec7</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
           <t>GRND7CONTINENTALCONNECTICUT</t>
@@ -13418,6 +13883,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2c094a3a-b444-426c-a3fa-cc121b33e13c</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr">
         <is>
           <t>GRND7CONTINENTALIOWA</t>
@@ -13555,6 +14025,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>51ba985f-1f85-4450-b499-6d6e5742650c</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr">
         <is>
           <t>GRND7CONTINENTALKENTUCKY</t>
@@ -13692,6 +14167,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>a9ee6ae7-f1b9-427d-93f8-3c493ce31c2b</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
           <t>GRND7CONTINENTALMICHIGAN</t>
@@ -13829,6 +14309,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>dea28770-f1a7-42da-8c24-24bfe7ce00ff</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr">
         <is>
           <t>GRND7CONTINENTALNEWJERSEY</t>
@@ -13966,6 +14451,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>644efc0a-0f3e-41c0-a3da-f27bbc2c1e62</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr">
         <is>
           <t>GRND7CONTINENTALNEWYORK</t>
@@ -14103,6 +14593,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>40f05451-8bdd-40f4-8fb2-580e6790f9d7</t>
+        </is>
+      </c>
       <c r="G111" t="inlineStr">
         <is>
           <t>GRND7CONTINENTALWISCONSIN</t>
@@ -14240,6 +14735,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>6874cb7d-df57-47d5-a139-2c3cd9a350a8</t>
+        </is>
+      </c>
       <c r="G112" t="inlineStr">
         <is>
           <t>GRND7CONTINENTALPENNSYLVANIA</t>
@@ -14374,6 +14874,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>8d3f2ab3-47c1-49c1-b8ec-7fb80d1a3fa5</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr">
         <is>
           <t>GRND7PACIFICCANTERBURY</t>
@@ -14511,6 +15016,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>97183f72-210b-4c0d-a373-7e9308718f87</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr">
         <is>
           <t>GRND7PACIFICGOLDENBAY</t>
@@ -14648,6 +15158,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>b3cbf076-151f-4b0c-a4d4-dd6f2ba103a1</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
           <t>GRND7PACIFICQUEENSTOWN</t>
@@ -14785,6 +15300,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>6205d42d-6b91-4233-8ed1-06689c1cb76f</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr">
         <is>
           <t>GRND7PACIFICWELLINGTON</t>
@@ -14932,6 +15452,11 @@
           <t>88006-2</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>f5c4314f-3e85-44f9-b149-056fe1da7e45</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr">
         <is>
           <t>GRND7PACIFIC880062</t>
@@ -15069,6 +15594,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>d7166002-eb03-47c3-8a80-b91918d6a625</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr">
         <is>
           <t>GRND7ANCHOR7BATTERYPOINT</t>
@@ -15206,6 +15736,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>de01fba1-041c-4110-9035-2c64f7e2025b</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
           <t>GRND7ANCHOR7NORTHHEAD</t>
@@ -15343,6 +15878,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>e3a643ed-2fdc-4c67-93a3-af7baaff19fd</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr">
         <is>
           <t>GRND7ANCHOR7OAKISLAND</t>
@@ -15480,6 +16020,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>74953b54-82b4-4e71-9081-aaabd0616a54</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr">
         <is>
           <t>GRND7ANCHOR7PEGGYSCOVE</t>
@@ -15617,6 +16162,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>dbb06d24-ac53-44c7-a67e-b28371fa0a8e</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
           <t>GRND7ANCHOR7POINTREYES</t>
@@ -15754,6 +16304,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>bfc0b7c0-d6cc-41de-b515-cb3f88a59d5f</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
           <t>GRND7ANCHOR7SAMBRO</t>
@@ -15891,6 +16446,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>9be8b504-13c0-47ef-9dbd-079403167f0f</t>
+        </is>
+      </c>
       <c r="G124" t="inlineStr">
         <is>
           <t>GRND7ANCHOR7WINDPOINT</t>
@@ -16028,6 +16588,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>a5a43a51-979e-41b2-8621-5de2ad9c58ae</t>
+        </is>
+      </c>
       <c r="G125" t="inlineStr">
         <is>
           <t>GRND7WONDER7ALEXANDRIA</t>
@@ -16165,6 +16730,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>4a42af64-7f68-4d0e-aeb0-2c3a624a658f</t>
+        </is>
+      </c>
       <c r="G126" t="inlineStr">
         <is>
           <t>GRND7WONDER7BABYLON</t>
@@ -16302,6 +16872,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>92de1677-ce49-436d-8242-b6b05429051b</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
           <t>GRND7WONDER7COLISEUM</t>
@@ -16439,6 +17014,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>5d3e9397-b057-4727-a98a-1f2367aaedb8</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
           <t>GRND7WONDER7GIZA</t>
@@ -16576,6 +17156,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>70a85fa5-db40-488f-a6be-a4726afb61ad</t>
+        </is>
+      </c>
       <c r="G129" t="inlineStr">
         <is>
           <t>GRND7WONDER7OLYMPIA</t>
@@ -16713,6 +17298,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>1148ed5a-b219-4103-9d79-7fa556a926ea</t>
+        </is>
+      </c>
       <c r="G130" t="inlineStr">
         <is>
           <t>GRND7WONDER7PETRA</t>
@@ -16850,6 +17440,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>ff729b58-9ead-416a-9fd2-30b9922cbcd8</t>
+        </is>
+      </c>
       <c r="G131" t="inlineStr">
         <is>
           <t>GRND7WONDER7RHODES</t>
@@ -17121,6 +17716,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>849bf0d3-5502-46e5-9bef-39ea2806be0e</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
           <t>GRND7INOV8FLOWERPOTISLAND</t>
@@ -17260,6 +17860,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>14a768e0-b279-4809-bb10-34f3382d21d7</t>
+        </is>
+      </c>
       <c r="G134" t="inlineStr">
         <is>
           <t>GRND7INOV8LIONSHEAD</t>
@@ -17399,6 +18004,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>564e0079-9e09-42b6-809f-ca2533d59498</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
           <t>GRND7INOV8MANITOULIN</t>
@@ -17538,6 +18148,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>48174a6a-6f6e-4f37-8d86-fc23a238a0d0</t>
+        </is>
+      </c>
       <c r="G136" t="inlineStr">
         <is>
           <t>GRND7INOV8MERMAIDSCOVE</t>
@@ -17677,6 +18292,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>387ff3e5-fa0b-4dbb-91b0-4eab2b3a6841</t>
+        </is>
+      </c>
       <c r="G137" t="inlineStr">
         <is>
           <t>GRND7INOV8PENINSULA</t>
@@ -17950,6 +18570,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>89293851-0188-4e07-b336-436f6887852d</t>
+        </is>
+      </c>
       <c r="G139" t="inlineStr">
         <is>
           <t>GRND7INOV8TOBERMORY</t>
@@ -18089,6 +18714,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>c1b533bf-70df-41e7-86c2-feb6e6af1c28</t>
+        </is>
+      </c>
       <c r="G140" t="inlineStr">
         <is>
           <t>GRND5DESIGNERALEXANDRIAHB</t>
@@ -18223,6 +18853,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>9b07aae7-e965-47ed-9f0e-ca56abac892a</t>
+        </is>
+      </c>
       <c r="G141" t="inlineStr">
         <is>
           <t>GRND5DESIGNERNORTHHEADHB</t>
@@ -18357,6 +18992,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>e89a4c08-17b3-4557-a409-37e23d5457ac</t>
+        </is>
+      </c>
       <c r="G142" t="inlineStr">
         <is>
           <t>GRND5DESIGNERRHODESHB</t>
@@ -18491,6 +19131,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>6b5d0150-1fac-48f7-9762-ee16e9d56c81</t>
+        </is>
+      </c>
       <c r="G143" t="inlineStr">
         <is>
           <t>GRND5DESIGNERRICELAKEHB</t>
@@ -18625,6 +19270,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>ff91b7bd-620f-4704-a833-a68ec47e2b71</t>
+        </is>
+      </c>
       <c r="G144" t="inlineStr">
         <is>
           <t>GRND5DESIGNERSAMBROHB</t>
@@ -18759,6 +19409,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>f1d38e8a-2241-496b-8bd2-7669898dde31</t>
+        </is>
+      </c>
       <c r="G145" t="inlineStr">
         <is>
           <t>GRND5DESIGNERWINDPOINTHB</t>
@@ -18893,6 +19548,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>5018185a-74ee-4255-9065-c33b658a5b4c</t>
+        </is>
+      </c>
       <c r="G146" t="inlineStr">
         <is>
           <t>GRND9BLISSAUGUSTDUSK</t>
@@ -19022,6 +19682,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>13173d91-2eee-414b-9b01-859ab06e32b9</t>
+        </is>
+      </c>
       <c r="G147" t="inlineStr">
         <is>
           <t>GRND9BLISSCAMPFIRE</t>
@@ -19151,6 +19816,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>16cf1a1e-c8db-43b4-9973-7959c6aefac6</t>
+        </is>
+      </c>
       <c r="G148" t="inlineStr">
         <is>
           <t>GRND9BLISSGAZEBO</t>
@@ -19280,6 +19950,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>3cf270f5-cc7d-4974-8bd6-24977744da96</t>
+        </is>
+      </c>
       <c r="G149" t="inlineStr">
         <is>
           <t>GRND9BLISSHIKINGTRAIL</t>
@@ -19409,6 +20084,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>ee0a8158-7317-4f17-bcc5-03ba29a7c48f</t>
+        </is>
+      </c>
       <c r="G150" t="inlineStr">
         <is>
           <t>GRND9BLISSMORNINGDEW</t>
@@ -19538,6 +20218,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>db9409fa-3929-4460-902b-778ce3e12490</t>
+        </is>
+      </c>
       <c r="G151" t="inlineStr">
         <is>
           <t>GRND9BLISSSTARLIGHT</t>
@@ -19667,6 +20352,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>f8bab8e3-c075-43f4-92e7-bdad59fccd27</t>
+        </is>
+      </c>
       <c r="G152" t="inlineStr">
         <is>
           <t>GRND9BLISSSEABREEZE</t>
@@ -19796,6 +20486,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>386ec63f-deac-476a-b932-89f32cc7517b</t>
+        </is>
+      </c>
       <c r="G153" t="inlineStr">
         <is>
           <t>GRND9BLISSSUMMERSHADE</t>
@@ -19925,6 +20620,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>7e167c3a-279f-4d44-b109-fd7d91a35e7e</t>
+        </is>
+      </c>
       <c r="G154" t="inlineStr">
         <is>
           <t>GRND9BLISSTREEHOUSE</t>
@@ -20054,6 +20754,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>222edac6-cbfb-42f4-8822-a3e97b606672</t>
+        </is>
+      </c>
       <c r="G155" t="inlineStr">
         <is>
           <t>GRND9BLISSWOODLAND</t>
@@ -21017,6 +21722,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>e60b1cd8-66bf-4964-a412-cccf82e2a99e</t>
+        </is>
+      </c>
       <c r="G162" t="inlineStr">
         <is>
           <t>GRND9SUPREMEXAUTUMNBLAZE</t>
@@ -21146,6 +21856,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>9716055a-a906-484f-a293-564aada58aa7</t>
+        </is>
+      </c>
       <c r="G163" t="inlineStr">
         <is>
           <t>GRND9SUPREMEXARCTICWHISPER</t>
@@ -21275,6 +21990,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>a6d7c9f3-4638-4286-a4dc-b770d8730ae7</t>
+        </is>
+      </c>
       <c r="G164" t="inlineStr">
         <is>
           <t>GRND9SUPREMEXBUTTERCUP</t>
@@ -21404,6 +22124,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>a20f5a86-b71f-47e2-9d84-b59c86b300a7</t>
+        </is>
+      </c>
       <c r="G165" t="inlineStr">
         <is>
           <t>GRND9SUPREMEXCITRUSLEAF</t>
@@ -21533,6 +22258,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>13781b1b-4d4c-4f8b-b91a-d591c45e1119</t>
+        </is>
+      </c>
       <c r="G166" t="inlineStr">
         <is>
           <t>GRND9SUPREMEXEBONYECLIPSE</t>
@@ -21662,6 +22392,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>1f8de4e2-9a21-4d1c-8f98-8f4a5adf168e</t>
+        </is>
+      </c>
       <c r="G167" t="inlineStr">
         <is>
           <t>GRND9SUPREMEXLEMONZEST</t>
@@ -21791,6 +22526,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>8ee7ec39-1166-42b4-b66c-f4cf0fc2edaf</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr">
         <is>
           <t>GRND9SUPREMEXSUNBEAM</t>
@@ -21920,6 +22660,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>97983729-319d-44ed-9d2f-365c9969b892</t>
+        </is>
+      </c>
       <c r="G169" t="inlineStr">
         <is>
           <t>GRND9SUPREMEXTOFFEEAPPLE</t>
@@ -22049,6 +22794,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>c63cbf8b-7eac-4320-a411-194fbd5a0096</t>
+        </is>
+      </c>
       <c r="G170" t="inlineStr">
         <is>
           <t>GRND7ESSENTIALALGONQUIN</t>
@@ -22177,6 +22927,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>4f7a74af-ba15-43dc-9a03-c0026e07af0f</t>
+        </is>
+      </c>
       <c r="G171" t="inlineStr">
         <is>
           <t>GRND7ESSENTIALGEORGIANBAY</t>
@@ -22300,6 +23055,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>0f0b562c-dfca-43d0-ae21-f882b8882415</t>
+        </is>
+      </c>
       <c r="G172" t="inlineStr">
         <is>
           <t>GRND7ESSENTIALKAWARTHA</t>
@@ -22423,6 +23183,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>b7d2c0ea-ff34-4eba-9d00-94683304a6c0</t>
+        </is>
+      </c>
       <c r="G173" t="inlineStr">
         <is>
           <t>GRND7ESSENTIALLAKESIMCOE</t>
@@ -22546,6 +23311,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>17f13329-a8e6-444b-93c8-54901d98e7f1</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr">
         <is>
           <t>GRND7ESSENTIALMUSKOKA</t>
@@ -22669,6 +23439,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>6e7fe265-0a69-46d0-b502-334f963a0524</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr">
         <is>
           <t>GRND7ESSENTIALSANDBANKS</t>
@@ -22792,6 +23567,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>c42ddacd-bef2-4281-b50d-968c742503f3</t>
+        </is>
+      </c>
       <c r="G176" t="inlineStr">
         <is>
           <t>GRND24ESSENTIALFLAGSTONE</t>
@@ -22915,6 +23695,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>20b510e0-fd47-4f6d-8913-0952fc0107cf</t>
+        </is>
+      </c>
       <c r="G177" t="inlineStr">
         <is>
           <t>GRND24ESSENTIALHEARTHSTONE</t>
@@ -23038,6 +23823,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>41a5a4d3-367a-4d57-9314-1646997a6fd2</t>
+        </is>
+      </c>
       <c r="G178" t="inlineStr">
         <is>
           <t>GRND24ESSENTIALTOUCHSTONE</t>
@@ -23161,6 +23951,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>091f95e3-9aee-4b70-817b-cbd930752b0d</t>
+        </is>
+      </c>
       <c r="G179" t="inlineStr">
         <is>
           <t>GRND7ENTREPRENEURCANVASLIGHT</t>
@@ -23292,6 +24087,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>8e70dfbd-b3d9-41a5-b902-1d2476f5d581</t>
+        </is>
+      </c>
       <c r="G180" t="inlineStr">
         <is>
           <t>GRND7ENTREPRENEURCHROMADRIFT</t>
@@ -23423,6 +24223,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>6548de12-95e4-4d66-866b-672a165aca9b</t>
+        </is>
+      </c>
       <c r="G181" t="inlineStr">
         <is>
           <t>GRND7ENTREPRENEURFEATHERGRASS</t>
@@ -23554,6 +24359,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>ad49e30c-695a-4034-892d-6be1c16a6dec</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr">
         <is>
           <t>GRND7ENTREPRENEURRAINMOOR</t>
@@ -23685,6 +24495,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>cca5474f-8a76-4574-b848-b2d019389b70</t>
+        </is>
+      </c>
       <c r="G183" t="inlineStr">
         <is>
           <t>GRND7ENTREPRENEURSTONEVEIL</t>
@@ -23816,6 +24631,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>7f41ed68-c48a-4022-b49c-e440b886ba7e</t>
+        </is>
+      </c>
       <c r="G184" t="inlineStr">
         <is>
           <t>GRND7ENTREPRENEURWOODMERE</t>
@@ -23947,6 +24767,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>41d3aed6-793d-4da8-a710-49ba3e2a2fe0</t>
+        </is>
+      </c>
       <c r="G185" t="inlineStr">
         <is>
           <t>GRND7TIMELESSACACIA</t>
@@ -24070,6 +24895,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>95ca80de-00ef-420d-af53-476ed24968f1</t>
+        </is>
+      </c>
       <c r="G186" t="inlineStr">
         <is>
           <t>GRND7TIMELESSAPPALACHIANMOUNTAINS</t>
@@ -24193,6 +25023,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>0a6f6e36-8b89-11eb-f3d6-7e8b1f0c0e39</t>
+        </is>
+      </c>
       <c r="G187" t="inlineStr">
         <is>
           <t>GRND7TIMELESSBARNBOARD</t>
@@ -24316,6 +25151,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>c6236040-bdce-49da-887e-b20d54fe4347</t>
+        </is>
+      </c>
       <c r="G188" t="inlineStr">
         <is>
           <t>GRND7TIMELESSCLOUDYSKY</t>
@@ -24439,6 +25279,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>dc884c17-07d5-4d83-82a7-185243800de0</t>
+        </is>
+      </c>
       <c r="G189" t="inlineStr">
         <is>
           <t>GRND7TIMELESSEXOTICWALNUT</t>
@@ -24562,6 +25407,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>e4fbe49e-44bb-4e45-9f33-0e303f565314</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr">
         <is>
           <t>GRND7TIMELESSHAZE</t>
@@ -24685,6 +25535,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>1c8046e4-3772-4a4c-ba75-afe195e090f7</t>
+        </is>
+      </c>
       <c r="G191" t="inlineStr">
         <is>
           <t>GRND7TIMELESSHAZELNUT</t>
@@ -24808,6 +25663,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>efcc8b00-e172-465f-a1c6-b6c4c04f6779</t>
+        </is>
+      </c>
       <c r="G192" t="inlineStr">
         <is>
           <t>GRND7TIMELESSNORTHERNOAK</t>
@@ -24931,6 +25791,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>db2ff98c-bd4d-4a13-9fb3-587f3801af9e</t>
+        </is>
+      </c>
       <c r="G193" t="inlineStr">
         <is>
           <t>GRND7TIMELESSSMOKEDOAK</t>
@@ -25054,6 +25919,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>659cdd77-6ffa-4151-94a0-5e78de73404b</t>
+        </is>
+      </c>
       <c r="G194" t="inlineStr">
         <is>
           <t>GRND7TIMELESSWEATHEREDOAK</t>
@@ -25177,6 +26047,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>a14fe2ac-7795-4112-af8f-4ba3f709e0ec</t>
+        </is>
+      </c>
       <c r="G195" t="inlineStr">
         <is>
           <t>GRND7ULTIMATEFRIDAYHARBOR</t>
@@ -25305,6 +26180,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2e2a3059-6889-4404-ad37-3923342f6c4b</t>
+        </is>
+      </c>
       <c r="G196" t="inlineStr">
         <is>
           <t>GRND7ULTIMATEHUMBERBAY</t>
@@ -25433,6 +26313,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>c236a9ad-b17a-4cdb-8671-5793137e8b58</t>
+        </is>
+      </c>
       <c r="G197" t="inlineStr">
         <is>
           <t>GRND7ULTIMATEHIGHPARK</t>
@@ -25561,6 +26446,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>bab57cfe-2a3b-411d-822e-3a9b4d2dc6c9</t>
+        </is>
+      </c>
       <c r="G198" t="inlineStr">
         <is>
           <t>GRND7ULTIMATELAKESHOREBLVD</t>
@@ -25689,6 +26579,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>ec1fd64e-e983-409f-b84f-afcca3b8bf93</t>
+        </is>
+      </c>
       <c r="G199" t="inlineStr">
         <is>
           <t>GRND7ULTIMATELAKEVIEW</t>
@@ -25817,6 +26712,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>aef103e4-ccae-4294-a0a2-c30c92c65c0c</t>
+        </is>
+      </c>
       <c r="G200" t="inlineStr">
         <is>
           <t>GRND7ULTIMATEPIER17</t>
@@ -25945,6 +26845,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>f184bf18-c17e-4ae5-a643-7f5131508727</t>
+        </is>
+      </c>
       <c r="G201" t="inlineStr">
         <is>
           <t>GRND7ULTIMATESUNNYSIDE</t>
@@ -26073,6 +26978,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>81264d25-47f1-4b97-b69a-057b0b87123a</t>
+        </is>
+      </c>
       <c r="G202" t="inlineStr">
         <is>
           <t>GRND7ULTIMATESUMMERWHARF</t>
@@ -26201,6 +27111,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2f89c497-fd75-4511-883a-05cd91767932</t>
+        </is>
+      </c>
       <c r="G203" t="inlineStr">
         <is>
           <t>GRND12ULTIMATEARCHBRIDGE</t>
@@ -26329,6 +27244,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2af1d997-ee2f-40f6-b0ae-931a12ab915d</t>
+        </is>
+      </c>
       <c r="G204" t="inlineStr">
         <is>
           <t>GRND12ULTIMATESKYLINE</t>
@@ -26457,6 +27377,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>4c6a39de-71fb-4cb8-bfdf-c57e02ae0cd1</t>
+        </is>
+      </c>
       <c r="G205" t="inlineStr">
         <is>
           <t>GRND12MM12COLLECTIONARLESNATURAL</t>
@@ -26569,6 +27494,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>1da3161b-1388-43c1-891d-96ea6c5a9880</t>
+        </is>
+      </c>
       <c r="G206" t="inlineStr">
         <is>
           <t>GRND12MM12COLLECTIONFADOGAVIA</t>
@@ -26681,6 +27611,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>63ca2876-8e3e-4539-9588-e4fa05915b37</t>
+        </is>
+      </c>
       <c r="G207" t="inlineStr">
         <is>
           <t>GRND12MM12COLLECTIONFADOSOTAVENTO</t>
@@ -26793,6 +27728,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>8fa820bd-016f-4d13-8a67-66484c08ad21</t>
+        </is>
+      </c>
       <c r="G208" t="inlineStr">
         <is>
           <t>GRND12MM12COLLECTIONKALASALBAR</t>
@@ -26905,6 +27845,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>d4821c00-fa71-4b27-9d96-25c9eab72776</t>
+        </is>
+      </c>
       <c r="G209" t="inlineStr">
         <is>
           <t>GRND12MM12COLLECTIONKALMARGRIS</t>
@@ -27017,6 +27962,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>e894d55a-4aeb-4347-af4e-823e6cd6c89e</t>
+        </is>
+      </c>
       <c r="G210" t="inlineStr">
         <is>
           <t>GRND12MM12COLLECTIONKALASNOZ</t>
@@ -27129,6 +28079,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>26be438f-5a00-4070-9f32-21c32cbc57ac</t>
+        </is>
+      </c>
       <c r="G211" t="inlineStr">
         <is>
           <t>GRND12MM12COLLECTIONROBLETWILIGHT</t>
@@ -27241,6 +28196,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>7ecc043a-a328-4c2f-9d9f-76d41b3131f5</t>
+        </is>
+      </c>
       <c r="G212" t="inlineStr">
         <is>
           <t>GRND12MM12COLLECTIONVIENADORADO</t>
@@ -27353,6 +28313,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>af323a25-3573-4aa2-8591-be9a4dc945b2</t>
+        </is>
+      </c>
       <c r="G213" t="inlineStr">
         <is>
           <t>GRND12MM12COLLECTIONWEXFORDTOSTADO</t>
@@ -27465,6 +28430,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>bf45a1e2-c25a-455d-ac66-a1ad76055c4d</t>
+        </is>
+      </c>
       <c r="G214" t="inlineStr">
         <is>
           <t>GRND12MMXXLANETO</t>
@@ -27577,6 +28547,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>09d9ea1d-4b58-48be-9d22-be86a4b09c95</t>
+        </is>
+      </c>
       <c r="G215" t="inlineStr">
         <is>
           <t>GRND12MMXXLCERVINO</t>
@@ -27689,6 +28664,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>647cc626-ecd3-4247-a410-bc4b450e16c6</t>
+        </is>
+      </c>
       <c r="G216" t="inlineStr">
         <is>
           <t>GRND12MMXXLDENALI</t>
@@ -27801,6 +28781,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>93467ac7-fe31-4438-b7af-9e61813b38fb</t>
+        </is>
+      </c>
       <c r="G217" t="inlineStr">
         <is>
           <t>GRND12MMXXLELGON</t>
@@ -27913,6 +28898,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>338fca1f-b24c-4639-8080-05e48ef69a0e</t>
+        </is>
+      </c>
       <c r="G218" t="inlineStr">
         <is>
           <t>GRND12MMXXLEVEREST</t>
@@ -28025,6 +29015,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>50d6240e-7385-4d3f-bd60-4a0ae4b39b5e</t>
+        </is>
+      </c>
       <c r="G219" t="inlineStr">
         <is>
           <t>GRND12MMXXLFUJI</t>
@@ -28137,6 +29132,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>1d5d34e6-5333-45ee-bd21-a40387493d72</t>
+        </is>
+      </c>
       <c r="G220" t="inlineStr">
         <is>
           <t>GRND12MMXXLKILIMANJARO</t>
@@ -28249,6 +29249,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>ed8e65a6-0a53-434b-9eed-81fc631d4be3</t>
+        </is>
+      </c>
       <c r="G221" t="inlineStr">
         <is>
           <t>GRND12MMXXLKINGPEAK</t>
@@ -28361,6 +29366,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>d4ea4b8e-4285-454d-880c-fcef82976d66</t>
+        </is>
+      </c>
       <c r="G222" t="inlineStr">
         <is>
           <t>GRND12MMXXLLOGAN</t>
@@ -28473,6 +29483,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>cca6201f-baa3-43fd-9d9a-e1252127d132</t>
+        </is>
+      </c>
       <c r="G223" t="inlineStr">
         <is>
           <t>GRND12MMXXLMONTBLANC</t>
@@ -28585,6 +29600,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>9a41372f-3d13-47f1-808e-9addf592b8d5</t>
+        </is>
+      </c>
       <c r="G224" t="inlineStr">
         <is>
           <t>GRND12MMAQUAMATEADELAIDE</t>
@@ -28710,6 +29730,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>aca0fdd0-7677-4449-a9d4-d3f937d41a49</t>
+        </is>
+      </c>
       <c r="G225" t="inlineStr">
         <is>
           <t>GRND12MMAQUAMATEALICESPRINGS</t>
@@ -28835,6 +29860,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>f5f15bea-e4bf-400d-9244-a24bb56d9546</t>
+        </is>
+      </c>
       <c r="G226" t="inlineStr">
         <is>
           <t>GRND12MMAQUAMATEBRISBANE</t>
@@ -28960,6 +29990,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>18f2e9b5-73eb-4178-852e-e5a68b4305de</t>
+        </is>
+      </c>
       <c r="G227" t="inlineStr">
         <is>
           <t>GRND12MMAQUAMATECAIRNS</t>
@@ -29085,6 +30120,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>19b2fdae-5ef1-432a-8574-7b930dccffbe</t>
+        </is>
+      </c>
       <c r="G228" t="inlineStr">
         <is>
           <t>GRND12MMAQUAMATECANBERRA</t>
@@ -29210,6 +30250,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>94b8492b-5c24-41ad-84d8-f687a1a6d215</t>
+        </is>
+      </c>
       <c r="G229" t="inlineStr">
         <is>
           <t>GRND12MMAQUAMATEDARWIN</t>
@@ -29335,6 +30380,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>b172256c-158a-4c0b-8770-968029069c6a</t>
+        </is>
+      </c>
       <c r="G230" t="inlineStr">
         <is>
           <t>GRND12MMAQUAMATEHOBART</t>
@@ -29460,6 +30510,11 @@
           <t>Grandeur</t>
         </is>
       </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>c0ec0244-b58d-469b-9efc-3cfc96a47001</t>
+        </is>
+      </c>
       <c r="G231" t="inlineStr">
         <is>
           <t>GRND12MMAQUAMATEMELBOURNE</t>
@@ -29583,6 +30638,11 @@
       <c r="D232" t="inlineStr">
         <is>
           <t>Grandeur</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>ccf820a0-b109-4db9-9cb5-dacf2bcfcbe6</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">

--- a/ingest/2026-09-03/grandeur_airtable_upload_2026-09-03.xlsx
+++ b/ingest/2026-09-03/grandeur_airtable_upload_2026-09-03.xlsx
@@ -13581,12 +13581,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GRNDLVP-0002</t>
+          <t>SPC-GRAN-0001</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Grandeur 7" Atlantic — 8936</t>
+          <t>Grandeur 7" Atlantic — GF8936</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -13601,12 +13601,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>GF8936</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>3f1ed949-8615-4feb-b12c-ec27fcec7287</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>GRND7ATLANTIC8936</t>
+          <t>GRND7ATLANTICGF8936</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -13706,12 +13711,17 @@
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>AMBIGUOUS MATCH — could not be reconciled against the live catalogue with confidence; SKU below is the run-generated placeholder, NOT a real catalogue SKU. Colour placeholder "8936" vs live "GF8936" (SPC-GRAN-0001, Supplier SKU GF8936). Partial supplier-code match only — not confident enough to adopt. Confirm with Grandeur, then either adopt SPC-GRAN-0001 or keep as new. Resolve before import. | Colour name not provided by supplier -- product identified only by code '8936'. Used as colour placeholder; confirm actual colour name with Grandeur. SALE item, no regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 4.0mm SPC + 1mm underpad (material not named). *Two-side Closed Treads Available.</t>
+          <t>Resolved 2026-09-03 (Albert): adopted live SPC-GRAN-0001 — price-list code "8936" confirmed as the same product as live "GF8936". SKU, LS handle, Lightspeed ID and Supplier SKU taken from the live record per RULE 0. Colour name not provided by supplier -- product identified only by code '8936'. Used as colour placeholder; confirm actual colour name with Grandeur. SALE item, no regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 4.0mm SPC + 1mm underpad (material not named). *Two-side Closed Treads Available.</t>
+        </is>
+      </c>
+      <c r="BE104" t="inlineStr">
+        <is>
+          <t>rec71K5yB4qVmqrnm</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>ambiguous</t>
+          <t>matched</t>
         </is>
       </c>
     </row>
